--- a/research/traditional_assets/database/data/estonia/estonia_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_green_renewable_energy.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07627191660638473</v>
+        <v>0.07615537277317196</v>
       </c>
       <c r="C2">
-        <v>1408.490270297094</v>
+        <v>1398.470531876749</v>
       </c>
       <c r="D2">
-        <v>1373.490270297094</v>
+        <v>1378.763531876749</v>
       </c>
       <c r="E2">
-        <v>-774.1000000000001</v>
+        <v>-758.8070000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.293</v>
       </c>
       <c r="G2">
         <v>35</v>
@@ -1445,28 +1445,28 @@
         <v>66.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7692379000000001</v>
       </c>
       <c r="N2">
-        <v>66.5</v>
+        <v>65.73076210000001</v>
       </c>
       <c r="O2">
-        <v>13.3</v>
+        <v>13.14615242</v>
       </c>
       <c r="P2">
-        <v>53.2</v>
+        <v>52.58460968000001</v>
       </c>
       <c r="Q2">
-        <v>98</v>
+        <v>97.38460968000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07627191660638473</v>
+        <v>0.07651815431633531</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5827120363206049</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>86.44919861592882</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07615537277317196</v>
+        <v>0.07603882893995918</v>
       </c>
       <c r="C3">
-        <v>1398.470531876749</v>
+        <v>1388.491440937776</v>
       </c>
       <c r="D3">
-        <v>1378.763531876749</v>
+        <v>1384.077440937776</v>
       </c>
       <c r="E3">
-        <v>-758.8070000000001</v>
+        <v>-743.5140000000001</v>
       </c>
       <c r="F3">
-        <v>15.293</v>
+        <v>30.58600000000001</v>
       </c>
       <c r="G3">
         <v>35</v>
@@ -1527,28 +1527,28 @@
         <v>66.5</v>
       </c>
       <c r="M3">
-        <v>0.7692379000000001</v>
+        <v>1.5384758</v>
       </c>
       <c r="N3">
-        <v>65.73076210000001</v>
+        <v>64.9615242</v>
       </c>
       <c r="O3">
-        <v>13.14615242</v>
+        <v>12.99230484</v>
       </c>
       <c r="P3">
-        <v>52.58460968000001</v>
+        <v>51.96921936</v>
       </c>
       <c r="Q3">
-        <v>97.38460968000001</v>
+        <v>96.76921935999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07651815431633531</v>
+        <v>0.07676941728567264</v>
       </c>
       <c r="T3">
-        <v>0.5827120363206049</v>
+        <v>0.5874784020015227</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>86.44919861592882</v>
+        <v>43.2245993079644</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07603882893995918</v>
+        <v>0.07592228510674642</v>
       </c>
       <c r="C4">
-        <v>1388.491440937776</v>
+        <v>1378.553469278374</v>
       </c>
       <c r="D4">
-        <v>1384.077440937776</v>
+        <v>1389.432469278374</v>
       </c>
       <c r="E4">
-        <v>-743.5140000000001</v>
+        <v>-728.2210000000001</v>
       </c>
       <c r="F4">
-        <v>30.58600000000001</v>
+        <v>45.879</v>
       </c>
       <c r="G4">
         <v>35</v>
@@ -1609,28 +1609,28 @@
         <v>66.5</v>
       </c>
       <c r="M4">
-        <v>1.5384758</v>
+        <v>2.3077137</v>
       </c>
       <c r="N4">
-        <v>64.9615242</v>
+        <v>64.19228630000001</v>
       </c>
       <c r="O4">
-        <v>12.99230484</v>
+        <v>12.83845726</v>
       </c>
       <c r="P4">
-        <v>51.96921936</v>
+        <v>51.35382904000001</v>
       </c>
       <c r="Q4">
-        <v>96.76921935999999</v>
+        <v>96.15382904000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07676941728567264</v>
+        <v>0.07702586093479012</v>
       </c>
       <c r="T4">
-        <v>0.5874784020015227</v>
+        <v>0.5923430432634903</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.2245993079644</v>
+        <v>28.81639953864294</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07592228510674642</v>
+        <v>0.07580574127353365</v>
       </c>
       <c r="C5">
-        <v>1378.553469278374</v>
+        <v>1368.657096026697</v>
       </c>
       <c r="D5">
-        <v>1389.432469278374</v>
+        <v>1394.829096026697</v>
       </c>
       <c r="E5">
-        <v>-728.2210000000001</v>
+        <v>-712.9280000000001</v>
       </c>
       <c r="F5">
-        <v>45.879</v>
+        <v>61.17200000000001</v>
       </c>
       <c r="G5">
         <v>35</v>
@@ -1691,28 +1691,28 @@
         <v>66.5</v>
       </c>
       <c r="M5">
-        <v>2.3077137</v>
+        <v>3.076951600000001</v>
       </c>
       <c r="N5">
-        <v>64.19228630000001</v>
+        <v>63.4230484</v>
       </c>
       <c r="O5">
-        <v>12.83845726</v>
+        <v>12.68460968</v>
       </c>
       <c r="P5">
-        <v>51.35382904000001</v>
+        <v>50.73843872</v>
       </c>
       <c r="Q5">
-        <v>96.15382904000001</v>
+        <v>95.53843871999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07702586093479012</v>
+        <v>0.07728764715993089</v>
       </c>
       <c r="T5">
-        <v>0.5923430432634903</v>
+        <v>0.5973090312184157</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.81639953864294</v>
+        <v>21.6122996539822</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07580574127353365</v>
+        <v>0.07568919744032089</v>
       </c>
       <c r="C6">
-        <v>1368.657096026697</v>
+        <v>1358.802807783753</v>
       </c>
       <c r="D6">
-        <v>1394.829096026697</v>
+        <v>1400.267807783752</v>
       </c>
       <c r="E6">
-        <v>-712.9280000000001</v>
+        <v>-697.6350000000001</v>
       </c>
       <c r="F6">
-        <v>61.17200000000001</v>
+        <v>76.46500000000002</v>
       </c>
       <c r="G6">
         <v>35</v>
@@ -1773,28 +1773,28 @@
         <v>66.5</v>
       </c>
       <c r="M6">
-        <v>3.076951600000001</v>
+        <v>3.846189500000001</v>
       </c>
       <c r="N6">
-        <v>63.4230484</v>
+        <v>62.6538105</v>
       </c>
       <c r="O6">
-        <v>12.68460968</v>
+        <v>12.5307621</v>
       </c>
       <c r="P6">
-        <v>50.73843872</v>
+        <v>50.1230484</v>
       </c>
       <c r="Q6">
-        <v>95.53843871999999</v>
+        <v>94.9230484</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07728764715993089</v>
+        <v>0.07755494467402199</v>
       </c>
       <c r="T6">
-        <v>0.5973090312184157</v>
+        <v>0.6023795662881815</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.6122996539822</v>
+        <v>17.28983972318576</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07568919744032089</v>
+        <v>0.07557265360710812</v>
       </c>
       <c r="C7">
-        <v>1358.802807783753</v>
+        <v>1348.991098769673</v>
       </c>
       <c r="D7">
-        <v>1400.267807783752</v>
+        <v>1405.749098769673</v>
       </c>
       <c r="E7">
-        <v>-697.6350000000001</v>
+        <v>-682.3420000000001</v>
       </c>
       <c r="F7">
-        <v>76.46500000000002</v>
+        <v>91.75800000000002</v>
       </c>
       <c r="G7">
         <v>35</v>
@@ -1855,28 +1855,28 @@
         <v>66.5</v>
       </c>
       <c r="M7">
-        <v>3.846189500000001</v>
+        <v>4.615427400000001</v>
       </c>
       <c r="N7">
-        <v>62.6538105</v>
+        <v>61.8845726</v>
       </c>
       <c r="O7">
-        <v>12.5307621</v>
+        <v>12.37691452</v>
       </c>
       <c r="P7">
-        <v>50.1230484</v>
+        <v>49.50765808</v>
       </c>
       <c r="Q7">
-        <v>94.9230484</v>
+        <v>94.30765808</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07755494467402199</v>
+        <v>0.07782792936926396</v>
       </c>
       <c r="T7">
-        <v>0.6023795662881815</v>
+        <v>0.607557985082836</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.28983972318576</v>
+        <v>14.40819976932147</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07557265360710812</v>
+        <v>0.07554010977389534</v>
       </c>
       <c r="C8">
-        <v>1348.991098769673</v>
+        <v>1335.236373663652</v>
       </c>
       <c r="D8">
-        <v>1405.749098769673</v>
+        <v>1407.287373663652</v>
       </c>
       <c r="E8">
-        <v>-682.3420000000001</v>
+        <v>-667.0490000000001</v>
       </c>
       <c r="F8">
-        <v>91.75800000000001</v>
+        <v>107.051</v>
       </c>
       <c r="G8">
         <v>35</v>
@@ -1937,45 +1937,45 @@
         <v>66.5</v>
       </c>
       <c r="M8">
-        <v>4.615427400000001</v>
+        <v>5.5452418</v>
       </c>
       <c r="N8">
-        <v>61.8845726</v>
+        <v>60.9547582</v>
       </c>
       <c r="O8">
-        <v>12.37691452</v>
+        <v>12.19095164</v>
       </c>
       <c r="P8">
-        <v>49.50765808</v>
+        <v>48.76380656</v>
       </c>
       <c r="Q8">
-        <v>94.30765808</v>
+        <v>93.56380655999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07782792936926396</v>
+        <v>0.07810678470311327</v>
       </c>
       <c r="T8">
-        <v>0.607557985082836</v>
+        <v>0.6128477677225368</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.40819976932147</v>
+        <v>11.99226334909327</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07554010977389533</v>
+        <v>0.07543556594068258</v>
       </c>
       <c r="C9">
-        <v>1335.236373663652</v>
+        <v>1324.907787596869</v>
       </c>
       <c r="D9">
-        <v>1407.287373663652</v>
+        <v>1412.251787596869</v>
       </c>
       <c r="E9">
-        <v>-667.0490000000001</v>
+        <v>-651.7560000000001</v>
       </c>
       <c r="F9">
-        <v>107.051</v>
+        <v>122.344</v>
       </c>
       <c r="G9">
         <v>35</v>
@@ -2019,28 +2019,28 @@
         <v>66.5</v>
       </c>
       <c r="M9">
-        <v>5.5452418</v>
+        <v>6.337419200000001</v>
       </c>
       <c r="N9">
-        <v>60.9547582</v>
+        <v>60.1625808</v>
       </c>
       <c r="O9">
-        <v>12.19095164</v>
+        <v>12.03251616</v>
       </c>
       <c r="P9">
-        <v>48.76380656</v>
+        <v>48.13006464</v>
       </c>
       <c r="Q9">
-        <v>93.56380655999999</v>
+        <v>92.93006464</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07810678470311327</v>
+        <v>0.07839170210943758</v>
       </c>
       <c r="T9">
-        <v>0.6128477677225368</v>
+        <v>0.6182525456370137</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.99226334909327</v>
+        <v>10.49323043045661</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07543556594068258</v>
+        <v>0.0754534221074698</v>
       </c>
       <c r="C10">
-        <v>1324.907787596869</v>
+        <v>1308.764383101446</v>
       </c>
       <c r="D10">
-        <v>1412.251787596869</v>
+        <v>1411.401383101446</v>
       </c>
       <c r="E10">
-        <v>-651.7560000000001</v>
+        <v>-636.4630000000002</v>
       </c>
       <c r="F10">
-        <v>122.344</v>
+        <v>137.637</v>
       </c>
       <c r="G10">
         <v>35</v>
@@ -2101,45 +2101,45 @@
         <v>66.5</v>
       </c>
       <c r="M10">
-        <v>6.337419200000001</v>
+        <v>7.3635795</v>
       </c>
       <c r="N10">
-        <v>60.1625808</v>
+        <v>59.1364205</v>
       </c>
       <c r="O10">
-        <v>12.03251616</v>
+        <v>11.8272841</v>
       </c>
       <c r="P10">
-        <v>48.13006464</v>
+        <v>47.3091364</v>
       </c>
       <c r="Q10">
-        <v>92.93006464</v>
+        <v>92.1091364</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07839170210943758</v>
+        <v>0.07868288143678001</v>
       </c>
       <c r="T10">
-        <v>0.6182525456370137</v>
+        <v>0.6237761098792812</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.49323043045661</v>
+        <v>9.030933936409594</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0754534221074698</v>
+        <v>0.07536247827425704</v>
       </c>
       <c r="C11">
-        <v>1308.764383101446</v>
+        <v>1297.813314477775</v>
       </c>
       <c r="D11">
-        <v>1411.401383101446</v>
+        <v>1415.743314477775</v>
       </c>
       <c r="E11">
-        <v>-636.4630000000002</v>
+        <v>-621.1700000000001</v>
       </c>
       <c r="F11">
-        <v>137.637</v>
+        <v>152.93</v>
       </c>
       <c r="G11">
         <v>35</v>
@@ -2183,28 +2183,28 @@
         <v>66.5</v>
       </c>
       <c r="M11">
-        <v>7.3635795</v>
+        <v>8.181755000000001</v>
       </c>
       <c r="N11">
-        <v>59.1364205</v>
+        <v>58.318245</v>
       </c>
       <c r="O11">
-        <v>11.8272841</v>
+        <v>11.663649</v>
       </c>
       <c r="P11">
-        <v>47.3091364</v>
+        <v>46.654596</v>
       </c>
       <c r="Q11">
-        <v>92.1091364</v>
+        <v>91.454596</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07868288143678001</v>
+        <v>0.07898053141584115</v>
       </c>
       <c r="T11">
-        <v>0.6237761098792812</v>
+        <v>0.6294224199935992</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.030933936409594</v>
+        <v>8.127840542768634</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07536247827425706</v>
+        <v>0.07534193444104427</v>
       </c>
       <c r="C12">
-        <v>1297.813314477774</v>
+        <v>1283.504840206203</v>
       </c>
       <c r="D12">
-        <v>1415.743314477774</v>
+        <v>1416.727840206202</v>
       </c>
       <c r="E12">
-        <v>-621.1700000000001</v>
+        <v>-605.8770000000002</v>
       </c>
       <c r="F12">
-        <v>152.93</v>
+        <v>168.223</v>
       </c>
       <c r="G12">
         <v>35</v>
@@ -2265,45 +2265,45 @@
         <v>66.5</v>
       </c>
       <c r="M12">
-        <v>8.181755000000003</v>
+        <v>9.1345089</v>
       </c>
       <c r="N12">
-        <v>58.318245</v>
+        <v>57.3654911</v>
       </c>
       <c r="O12">
-        <v>11.663649</v>
+        <v>11.47309822</v>
       </c>
       <c r="P12">
-        <v>46.654596</v>
+        <v>45.89239288</v>
       </c>
       <c r="Q12">
-        <v>91.454596</v>
+        <v>90.69239288</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07898053141584116</v>
+        <v>0.0792848701584767</v>
       </c>
       <c r="T12">
-        <v>0.6294224199935994</v>
+        <v>0.6351956134812726</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.127840542768634</v>
+        <v>7.280084865865093</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07534193444104427</v>
+        <v>0.0752573906078315</v>
       </c>
       <c r="C13">
-        <v>1283.504840206203</v>
+        <v>1272.277903077312</v>
       </c>
       <c r="D13">
-        <v>1416.727840206202</v>
+        <v>1420.793903077312</v>
       </c>
       <c r="E13">
-        <v>-605.8770000000002</v>
+        <v>-590.5840000000001</v>
       </c>
       <c r="F13">
-        <v>168.223</v>
+        <v>183.516</v>
       </c>
       <c r="G13">
         <v>35</v>
@@ -2347,28 +2347,28 @@
         <v>66.5</v>
       </c>
       <c r="M13">
-        <v>9.1345089</v>
+        <v>9.964918800000001</v>
       </c>
       <c r="N13">
-        <v>57.3654911</v>
+        <v>56.5350812</v>
       </c>
       <c r="O13">
-        <v>11.47309822</v>
+        <v>11.30701624</v>
       </c>
       <c r="P13">
-        <v>45.89239288</v>
+        <v>45.22806496</v>
       </c>
       <c r="Q13">
-        <v>90.69239288</v>
+        <v>90.02806495999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0792848701584767</v>
+        <v>0.07959612569071761</v>
       </c>
       <c r="T13">
-        <v>0.6351956134812726</v>
+        <v>0.6411000159118478</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.280084865865093</v>
+        <v>6.673411127043002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0752573906078315</v>
+        <v>0.07517284677461873</v>
       </c>
       <c r="C14">
-        <v>1272.277903077312</v>
+        <v>1261.074372637181</v>
       </c>
       <c r="D14">
-        <v>1420.793903077312</v>
+        <v>1424.883372637181</v>
       </c>
       <c r="E14">
-        <v>-590.5840000000001</v>
+        <v>-575.2910000000002</v>
       </c>
       <c r="F14">
-        <v>183.516</v>
+        <v>198.809</v>
       </c>
       <c r="G14">
         <v>35</v>
@@ -2429,28 +2429,28 @@
         <v>66.5</v>
       </c>
       <c r="M14">
-        <v>9.964918800000001</v>
+        <v>10.7953287</v>
       </c>
       <c r="N14">
-        <v>56.5350812</v>
+        <v>55.7046713</v>
       </c>
       <c r="O14">
-        <v>11.30701624</v>
+        <v>11.14093426</v>
       </c>
       <c r="P14">
-        <v>45.22806496</v>
+        <v>44.56373704</v>
       </c>
       <c r="Q14">
-        <v>90.02806495999999</v>
+        <v>89.36373703999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07959612569071761</v>
+        <v>0.07991453652255026</v>
       </c>
       <c r="T14">
-        <v>0.6411000159118478</v>
+        <v>0.6471401517316315</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.673411127043002</v>
+        <v>6.160071809578155</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07517284677461873</v>
+        <v>0.07520030294140598</v>
       </c>
       <c r="C15">
-        <v>1261.074372637181</v>
+        <v>1244.450711670541</v>
       </c>
       <c r="D15">
-        <v>1424.883372637181</v>
+        <v>1423.552711670541</v>
       </c>
       <c r="E15">
-        <v>-575.2910000000002</v>
+        <v>-559.998</v>
       </c>
       <c r="F15">
-        <v>198.809</v>
+        <v>214.102</v>
       </c>
       <c r="G15">
         <v>35</v>
@@ -2511,45 +2511,45 @@
         <v>66.5</v>
       </c>
       <c r="M15">
-        <v>10.7953287</v>
+        <v>11.8398406</v>
       </c>
       <c r="N15">
-        <v>55.7046713</v>
+        <v>54.6601594</v>
       </c>
       <c r="O15">
-        <v>11.14093426</v>
+        <v>10.93203188</v>
       </c>
       <c r="P15">
-        <v>44.56373704</v>
+        <v>43.72812752</v>
       </c>
       <c r="Q15">
-        <v>89.36373703999999</v>
+        <v>88.52812752</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07991453652255026</v>
+        <v>0.0802403522574488</v>
       </c>
       <c r="T15">
-        <v>0.6471401517316315</v>
+        <v>0.6533207558262941</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.160071809578155</v>
+        <v>5.616629669828493</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07520030294140598</v>
+        <v>0.07512375910819319</v>
       </c>
       <c r="C16">
-        <v>1244.450711670541</v>
+        <v>1232.873612518373</v>
       </c>
       <c r="D16">
-        <v>1423.552711670541</v>
+        <v>1427.268612518372</v>
       </c>
       <c r="E16">
-        <v>-559.998</v>
+        <v>-544.705</v>
       </c>
       <c r="F16">
-        <v>214.102</v>
+        <v>229.3950000000001</v>
       </c>
       <c r="G16">
         <v>35</v>
@@ -2593,28 +2593,28 @@
         <v>66.5</v>
       </c>
       <c r="M16">
-        <v>11.8398406</v>
+        <v>12.6855435</v>
       </c>
       <c r="N16">
-        <v>54.6601594</v>
+        <v>53.81445649999999</v>
       </c>
       <c r="O16">
-        <v>10.93203188</v>
+        <v>10.7628913</v>
       </c>
       <c r="P16">
-        <v>43.72812752</v>
+        <v>43.05156519999999</v>
       </c>
       <c r="Q16">
-        <v>88.52812752</v>
+        <v>87.85156519999998</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0802403522574488</v>
+        <v>0.08057383424493317</v>
       </c>
       <c r="T16">
-        <v>0.6533207558262941</v>
+        <v>0.6596467858996544</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.616629669828493</v>
+        <v>5.242187691839925</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07512375910819319</v>
+        <v>0.0750472152749804</v>
       </c>
       <c r="C17">
-        <v>1232.873612518373</v>
+        <v>1221.315963374832</v>
       </c>
       <c r="D17">
-        <v>1427.268612518372</v>
+        <v>1431.003963374832</v>
       </c>
       <c r="E17">
-        <v>-544.7050000000002</v>
+        <v>-529.412</v>
       </c>
       <c r="F17">
-        <v>229.395</v>
+        <v>244.688</v>
       </c>
       <c r="G17">
         <v>35</v>
@@ -2675,28 +2675,28 @@
         <v>66.5</v>
       </c>
       <c r="M17">
-        <v>12.6855435</v>
+        <v>13.5312464</v>
       </c>
       <c r="N17">
-        <v>53.8144565</v>
+        <v>52.9687536</v>
       </c>
       <c r="O17">
-        <v>10.7628913</v>
+        <v>10.59375072</v>
       </c>
       <c r="P17">
-        <v>43.0515652</v>
+        <v>42.37500288</v>
       </c>
       <c r="Q17">
-        <v>87.8515652</v>
+        <v>87.17500287999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08057383424493317</v>
+        <v>0.08091525627973858</v>
       </c>
       <c r="T17">
-        <v>0.6596467858996544</v>
+        <v>0.6661234357366662</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.242187691839927</v>
+        <v>4.914550961099932</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0750472152749804</v>
+        <v>0.07497067144176764</v>
       </c>
       <c r="C18">
-        <v>1221.315963374832</v>
+        <v>1209.77791735037</v>
       </c>
       <c r="D18">
-        <v>1431.003963374832</v>
+        <v>1434.75891735037</v>
       </c>
       <c r="E18">
-        <v>-529.412</v>
+        <v>-514.1190000000001</v>
       </c>
       <c r="F18">
-        <v>244.688</v>
+        <v>259.9810000000001</v>
       </c>
       <c r="G18">
         <v>35</v>
@@ -2757,28 +2757,28 @@
         <v>66.5</v>
       </c>
       <c r="M18">
-        <v>13.5312464</v>
+        <v>14.3769493</v>
       </c>
       <c r="N18">
-        <v>52.9687536</v>
+        <v>52.12305069999999</v>
       </c>
       <c r="O18">
-        <v>10.59375072</v>
+        <v>10.42461014</v>
       </c>
       <c r="P18">
-        <v>42.37500288</v>
+        <v>41.69844055999999</v>
       </c>
       <c r="Q18">
-        <v>87.17500287999999</v>
+        <v>86.49844055999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08091525627973858</v>
+        <v>0.08126490535152729</v>
       </c>
       <c r="T18">
-        <v>0.6661234357366662</v>
+        <v>0.6727561494251724</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.914550961099932</v>
+        <v>4.625459728094053</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07497067144176764</v>
+        <v>0.07525412760855489</v>
       </c>
       <c r="C19">
-        <v>1209.77791735037</v>
+        <v>1180.67730205173</v>
       </c>
       <c r="D19">
-        <v>1434.75891735037</v>
+        <v>1420.95130205173</v>
       </c>
       <c r="E19">
-        <v>-514.1190000000001</v>
+        <v>-498.8260000000001</v>
       </c>
       <c r="F19">
-        <v>259.9810000000001</v>
+        <v>275.2740000000001</v>
       </c>
       <c r="G19">
         <v>35</v>
@@ -2839,45 +2839,45 @@
         <v>66.5</v>
       </c>
       <c r="M19">
-        <v>14.3769493</v>
+        <v>15.9108372</v>
       </c>
       <c r="N19">
-        <v>52.12305069999999</v>
+        <v>50.5891628</v>
       </c>
       <c r="O19">
-        <v>10.42461014</v>
+        <v>10.11783256</v>
       </c>
       <c r="P19">
-        <v>41.69844055999999</v>
+        <v>40.47133024</v>
       </c>
       <c r="Q19">
-        <v>86.49844055999999</v>
+        <v>85.27133024</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08126490535152729</v>
+        <v>0.08162308244945718</v>
       </c>
       <c r="T19">
-        <v>0.6727561494251724</v>
+        <v>0.6795506366182762</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.625459728094053</v>
+        <v>4.179541224895443</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07525412760855489</v>
+        <v>0.07572958377534213</v>
       </c>
       <c r="C20">
-        <v>1180.67730205173</v>
+        <v>1142.811316595733</v>
       </c>
       <c r="D20">
-        <v>1420.95130205173</v>
+        <v>1398.378316595733</v>
       </c>
       <c r="E20">
-        <v>-498.8260000000001</v>
+        <v>-483.5330000000001</v>
       </c>
       <c r="F20">
-        <v>275.274</v>
+        <v>290.5670000000001</v>
       </c>
       <c r="G20">
         <v>35</v>
@@ -2921,45 +2921,45 @@
         <v>66.5</v>
       </c>
       <c r="M20">
-        <v>15.9108372</v>
+        <v>17.8117571</v>
       </c>
       <c r="N20">
-        <v>50.5891628</v>
+        <v>48.68824289999999</v>
       </c>
       <c r="O20">
-        <v>10.11783256</v>
+        <v>9.737648579999998</v>
       </c>
       <c r="P20">
-        <v>40.47133024</v>
+        <v>38.95059431999999</v>
       </c>
       <c r="Q20">
-        <v>85.27133024</v>
+        <v>83.75059431999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08162308244945718</v>
+        <v>0.0819901034263483</v>
       </c>
       <c r="T20">
-        <v>0.6795506366182761</v>
+        <v>0.6865128889272591</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.179541224895443</v>
+        <v>3.733489044716424</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07572958377534213</v>
+        <v>0.07570103994212934</v>
       </c>
       <c r="C21">
-        <v>1142.811316595733</v>
+        <v>1128.853222589455</v>
       </c>
       <c r="D21">
-        <v>1398.378316595733</v>
+        <v>1399.713222589455</v>
       </c>
       <c r="E21">
-        <v>-483.5330000000001</v>
+        <v>-468.2400000000001</v>
       </c>
       <c r="F21">
-        <v>290.5670000000001</v>
+        <v>305.8600000000001</v>
       </c>
       <c r="G21">
         <v>35</v>
@@ -3003,28 +3003,28 @@
         <v>66.5</v>
       </c>
       <c r="M21">
-        <v>17.8117571</v>
+        <v>18.74921800000001</v>
       </c>
       <c r="N21">
-        <v>48.68824289999999</v>
+        <v>47.75078199999999</v>
       </c>
       <c r="O21">
-        <v>9.737648579999998</v>
+        <v>9.550156399999999</v>
       </c>
       <c r="P21">
-        <v>38.95059431999999</v>
+        <v>38.2006256</v>
       </c>
       <c r="Q21">
-        <v>83.75059431999999</v>
+        <v>83.00062559999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0819901034263483</v>
+        <v>0.08236629992766167</v>
       </c>
       <c r="T21">
-        <v>0.6865128889272591</v>
+        <v>0.6936491975439665</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.733489044716424</v>
+        <v>3.546814592480603</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07570103994212934</v>
+        <v>0.07614289610891659</v>
       </c>
       <c r="C22">
-        <v>1128.853222589455</v>
+        <v>1093.177464235909</v>
       </c>
       <c r="D22">
-        <v>1399.713222589455</v>
+        <v>1379.330464235909</v>
       </c>
       <c r="E22">
-        <v>-468.2400000000001</v>
+        <v>-452.9470000000001</v>
       </c>
       <c r="F22">
-        <v>305.8600000000001</v>
+        <v>321.1530000000001</v>
       </c>
       <c r="G22">
         <v>35</v>
@@ -3085,45 +3085,45 @@
         <v>66.5</v>
       </c>
       <c r="M22">
-        <v>18.74921800000001</v>
+        <v>20.58590730000001</v>
       </c>
       <c r="N22">
-        <v>47.75078199999999</v>
+        <v>45.9140927</v>
       </c>
       <c r="O22">
-        <v>9.550156399999999</v>
+        <v>9.18281854</v>
       </c>
       <c r="P22">
-        <v>38.2006256</v>
+        <v>36.73127416</v>
       </c>
       <c r="Q22">
-        <v>83.00062559999999</v>
+        <v>81.53127416</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08236629992766167</v>
+        <v>0.08275202039103363</v>
       </c>
       <c r="T22">
-        <v>0.6936491975439665</v>
+        <v>0.7009661722016033</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.546814592480603</v>
+        <v>3.230365270322576</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07614289610891657</v>
+        <v>0.07613675227570381</v>
       </c>
       <c r="C23">
-        <v>1093.17746423591</v>
+        <v>1078.163807793866</v>
       </c>
       <c r="D23">
-        <v>1379.33046423591</v>
+        <v>1379.609807793867</v>
       </c>
       <c r="E23">
-        <v>-452.9470000000001</v>
+        <v>-437.6540000000001</v>
       </c>
       <c r="F23">
-        <v>321.153</v>
+        <v>336.446</v>
       </c>
       <c r="G23">
         <v>35</v>
@@ -3167,28 +3167,28 @@
         <v>66.5</v>
       </c>
       <c r="M23">
-        <v>20.5859073</v>
+        <v>21.5661886</v>
       </c>
       <c r="N23">
-        <v>45.9140927</v>
+        <v>44.9338114</v>
       </c>
       <c r="O23">
-        <v>9.18281854</v>
+        <v>8.986762279999999</v>
       </c>
       <c r="P23">
-        <v>36.73127416</v>
+        <v>35.94704912</v>
       </c>
       <c r="Q23">
-        <v>81.53127416</v>
+        <v>80.74704911999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08275202039103363</v>
+        <v>0.08314763112269719</v>
       </c>
       <c r="T23">
-        <v>0.7009661722016033</v>
+        <v>0.7084707615940513</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.230365270322576</v>
+        <v>3.083530485307914</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07613675227570381</v>
+        <v>0.07756580844249104</v>
       </c>
       <c r="C24">
-        <v>1078.163807793866</v>
+        <v>1000.805965113811</v>
       </c>
       <c r="D24">
-        <v>1379.609807793867</v>
+        <v>1317.544965113811</v>
       </c>
       <c r="E24">
-        <v>-437.6540000000001</v>
+        <v>-422.3610000000001</v>
       </c>
       <c r="F24">
-        <v>336.446</v>
+        <v>351.739</v>
       </c>
       <c r="G24">
         <v>35</v>
@@ -3249,45 +3249,45 @@
         <v>66.5</v>
       </c>
       <c r="M24">
-        <v>21.5661886</v>
+        <v>25.2900341</v>
       </c>
       <c r="N24">
-        <v>44.9338114</v>
+        <v>41.2099659</v>
       </c>
       <c r="O24">
-        <v>8.986762279999999</v>
+        <v>8.24199318</v>
       </c>
       <c r="P24">
-        <v>35.94704912</v>
+        <v>32.96797272</v>
       </c>
       <c r="Q24">
-        <v>80.74704911999999</v>
+        <v>77.76797271999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08314763112269719</v>
+        <v>0.08355351745778057</v>
       </c>
       <c r="T24">
-        <v>0.7084707615940513</v>
+        <v>0.7161702753863032</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.083530485307914</v>
+        <v>2.629494279724992</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07756580844249104</v>
+        <v>0.07762206460927827</v>
       </c>
       <c r="C25">
-        <v>1000.805965113811</v>
+        <v>983.1837627123584</v>
       </c>
       <c r="D25">
-        <v>1317.544965113811</v>
+        <v>1315.215762712359</v>
       </c>
       <c r="E25">
-        <v>-422.3610000000001</v>
+        <v>-407.068</v>
       </c>
       <c r="F25">
-        <v>351.739</v>
+        <v>367.0320000000001</v>
       </c>
       <c r="G25">
         <v>35</v>
@@ -3331,28 +3331,28 @@
         <v>66.5</v>
       </c>
       <c r="M25">
-        <v>25.2900341</v>
+        <v>26.38960080000001</v>
       </c>
       <c r="N25">
-        <v>41.2099659</v>
+        <v>40.11039919999999</v>
       </c>
       <c r="O25">
-        <v>8.24199318</v>
+        <v>8.022079839999998</v>
       </c>
       <c r="P25">
-        <v>32.96797272</v>
+        <v>32.08831935999999</v>
       </c>
       <c r="Q25">
-        <v>77.76797271999999</v>
+        <v>76.88831936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08355351745778057</v>
+        <v>0.08397008501220823</v>
       </c>
       <c r="T25">
-        <v>0.7161702753863032</v>
+        <v>0.7240724079625616</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.629494279724992</v>
+        <v>2.519932018069784</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07762206460927827</v>
+        <v>0.0784583207760655</v>
       </c>
       <c r="C26">
-        <v>983.1837627123585</v>
+        <v>934.2130577328044</v>
       </c>
       <c r="D26">
-        <v>1315.215762712359</v>
+        <v>1281.538057732804</v>
       </c>
       <c r="E26">
-        <v>-407.0680000000001</v>
+        <v>-391.7750000000001</v>
       </c>
       <c r="F26">
-        <v>367.032</v>
+        <v>382.325</v>
       </c>
       <c r="G26">
         <v>35</v>
@@ -3413,45 +3413,45 @@
         <v>66.5</v>
       </c>
       <c r="M26">
-        <v>26.3896008</v>
+        <v>28.98023500000001</v>
       </c>
       <c r="N26">
-        <v>40.1103992</v>
+        <v>37.51976499999999</v>
       </c>
       <c r="O26">
-        <v>8.02207984</v>
+        <v>7.503952999999999</v>
       </c>
       <c r="P26">
-        <v>32.08831936</v>
+        <v>30.01581199999999</v>
       </c>
       <c r="Q26">
-        <v>76.88831936</v>
+        <v>74.81581199999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08397008501220823</v>
+        <v>0.08439776103475399</v>
       </c>
       <c r="T26">
-        <v>0.7240724079625614</v>
+        <v>0.7321852640741868</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.519932018069784</v>
+        <v>2.294667382786923</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0784583207760655</v>
+        <v>0.07854577694285272</v>
       </c>
       <c r="C27">
-        <v>934.2130577328044</v>
+        <v>915.497374975365</v>
       </c>
       <c r="D27">
-        <v>1281.538057732804</v>
+        <v>1278.115374975365</v>
       </c>
       <c r="E27">
-        <v>-391.7750000000001</v>
+        <v>-376.4820000000001</v>
       </c>
       <c r="F27">
-        <v>382.325</v>
+        <v>397.6180000000001</v>
       </c>
       <c r="G27">
         <v>35</v>
@@ -3495,28 +3495,28 @@
         <v>66.5</v>
       </c>
       <c r="M27">
-        <v>28.98023500000001</v>
+        <v>30.13944440000001</v>
       </c>
       <c r="N27">
-        <v>37.51976499999999</v>
+        <v>36.3605556</v>
       </c>
       <c r="O27">
-        <v>7.503952999999999</v>
+        <v>7.27211112</v>
       </c>
       <c r="P27">
-        <v>30.01581199999999</v>
+        <v>29.08844448</v>
       </c>
       <c r="Q27">
-        <v>74.81581199999999</v>
+        <v>73.88844448</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08439776103475399</v>
+        <v>0.0848369958687199</v>
       </c>
       <c r="T27">
-        <v>0.7321852640741868</v>
+        <v>0.7405173865672076</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.294667382786923</v>
+        <v>2.206410944987426</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07854577694285272</v>
+        <v>0.07863323310963996</v>
       </c>
       <c r="C28">
-        <v>915.497374975365</v>
+        <v>896.799925860229</v>
       </c>
       <c r="D28">
-        <v>1278.115374975365</v>
+        <v>1274.710925860229</v>
       </c>
       <c r="E28">
-        <v>-376.4820000000001</v>
+        <v>-361.1890000000001</v>
       </c>
       <c r="F28">
-        <v>397.6180000000001</v>
+        <v>412.9110000000001</v>
       </c>
       <c r="G28">
         <v>35</v>
@@ -3577,28 +3577,28 @@
         <v>66.5</v>
       </c>
       <c r="M28">
-        <v>30.13944440000001</v>
+        <v>31.29865380000001</v>
       </c>
       <c r="N28">
-        <v>36.3605556</v>
+        <v>35.20134619999999</v>
       </c>
       <c r="O28">
-        <v>7.27211112</v>
+        <v>7.040269239999998</v>
       </c>
       <c r="P28">
-        <v>29.08844448</v>
+        <v>28.16107695999999</v>
       </c>
       <c r="Q28">
-        <v>73.88844448</v>
+        <v>72.96107695999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0848369958687199</v>
+        <v>0.08528826453375336</v>
       </c>
       <c r="T28">
-        <v>0.7405173865672076</v>
+        <v>0.7490777863888041</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.206410944987426</v>
+        <v>2.124692021099003</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07863323310963996</v>
+        <v>0.07872068927642718</v>
       </c>
       <c r="C29">
-        <v>896.799925860229</v>
+        <v>878.12056507047</v>
       </c>
       <c r="D29">
-        <v>1274.710925860229</v>
+        <v>1271.32456507047</v>
       </c>
       <c r="E29">
-        <v>-361.1890000000001</v>
+        <v>-345.8960000000001</v>
       </c>
       <c r="F29">
-        <v>412.9110000000001</v>
+        <v>428.2040000000001</v>
       </c>
       <c r="G29">
         <v>35</v>
@@ -3659,28 +3659,28 @@
         <v>66.5</v>
       </c>
       <c r="M29">
-        <v>31.29865380000001</v>
+        <v>32.45786320000001</v>
       </c>
       <c r="N29">
-        <v>35.20134619999999</v>
+        <v>34.04213679999999</v>
       </c>
       <c r="O29">
-        <v>7.040269239999998</v>
+        <v>6.80842736</v>
       </c>
       <c r="P29">
-        <v>28.16107695999999</v>
+        <v>27.23370943999999</v>
       </c>
       <c r="Q29">
-        <v>72.96107695999999</v>
+        <v>72.03370944</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08528826453375336</v>
+        <v>0.0857520684394822</v>
       </c>
       <c r="T29">
-        <v>0.7490777863888041</v>
+        <v>0.7578759750943338</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.124692021099003</v>
+        <v>2.04881016320261</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07872068927642718</v>
+        <v>0.08210254544321441</v>
       </c>
       <c r="C30">
-        <v>878.12056507047</v>
+        <v>744.3940842255256</v>
       </c>
       <c r="D30">
-        <v>1271.32456507047</v>
+        <v>1152.891084225526</v>
       </c>
       <c r="E30">
-        <v>-345.8960000000001</v>
+        <v>-330.603</v>
       </c>
       <c r="F30">
-        <v>428.2040000000001</v>
+        <v>443.4970000000001</v>
       </c>
       <c r="G30">
         <v>35</v>
@@ -3741,45 +3741,45 @@
         <v>66.5</v>
       </c>
       <c r="M30">
-        <v>32.45786320000001</v>
+        <v>39.91473000000001</v>
       </c>
       <c r="N30">
-        <v>34.04213679999999</v>
+        <v>26.58526999999999</v>
       </c>
       <c r="O30">
-        <v>6.80842736</v>
+        <v>5.317053999999998</v>
       </c>
       <c r="P30">
-        <v>27.23370943999999</v>
+        <v>21.26821599999999</v>
       </c>
       <c r="Q30">
-        <v>72.03370944</v>
+        <v>66.06821599999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0857520684394822</v>
+        <v>0.08622893724396397</v>
       </c>
       <c r="T30">
-        <v>0.7578759750943338</v>
+        <v>0.7669220001014277</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.04881016320261</v>
+        <v>1.666051605510046</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08210254544321441</v>
+        <v>0.08230360161000164</v>
       </c>
       <c r="C31">
-        <v>744.3940842255256</v>
+        <v>722.7511392366991</v>
       </c>
       <c r="D31">
-        <v>1152.891084225526</v>
+        <v>1146.541139236699</v>
       </c>
       <c r="E31">
-        <v>-330.6030000000001</v>
+        <v>-315.3100000000001</v>
       </c>
       <c r="F31">
-        <v>443.497</v>
+        <v>458.79</v>
       </c>
       <c r="G31">
         <v>35</v>
@@ -3823,28 +3823,28 @@
         <v>66.5</v>
       </c>
       <c r="M31">
-        <v>39.91473</v>
+        <v>41.2911</v>
       </c>
       <c r="N31">
-        <v>26.58527</v>
+        <v>25.2089</v>
       </c>
       <c r="O31">
-        <v>5.317054000000001</v>
+        <v>5.04178</v>
       </c>
       <c r="P31">
-        <v>21.268216</v>
+        <v>20.16712</v>
       </c>
       <c r="Q31">
-        <v>66.06821600000001</v>
+        <v>64.96711999999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08622893724396397</v>
+        <v>0.08671943087143093</v>
       </c>
       <c r="T31">
-        <v>0.7669220001014277</v>
+        <v>0.7762264829658674</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.666051605510046</v>
+        <v>1.610516551993045</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08230360161000164</v>
+        <v>0.08250465777678886</v>
       </c>
       <c r="C32">
-        <v>722.7511392366991</v>
+        <v>701.1777601109584</v>
       </c>
       <c r="D32">
-        <v>1146.541139236699</v>
+        <v>1140.260760110958</v>
       </c>
       <c r="E32">
-        <v>-315.3100000000001</v>
+        <v>-300.0170000000001</v>
       </c>
       <c r="F32">
-        <v>458.79</v>
+        <v>474.083</v>
       </c>
       <c r="G32">
         <v>35</v>
@@ -3905,28 +3905,28 @@
         <v>66.5</v>
       </c>
       <c r="M32">
-        <v>41.2911</v>
+        <v>42.66747</v>
       </c>
       <c r="N32">
-        <v>25.2089</v>
+        <v>23.83253</v>
       </c>
       <c r="O32">
-        <v>5.04178</v>
+        <v>4.766506</v>
       </c>
       <c r="P32">
-        <v>20.16712</v>
+        <v>19.066024</v>
       </c>
       <c r="Q32">
-        <v>64.96711999999999</v>
+        <v>63.866024</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08671943087143093</v>
+        <v>0.08722414170549113</v>
       </c>
       <c r="T32">
-        <v>0.7762264829658674</v>
+        <v>0.7858006609857978</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.610516551993045</v>
+        <v>1.558564405154559</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08250465777678886</v>
+        <v>0.08270571394357609</v>
       </c>
       <c r="C33">
-        <v>701.1777601109584</v>
+        <v>679.6728098986877</v>
       </c>
       <c r="D33">
-        <v>1140.260760110958</v>
+        <v>1134.048809898688</v>
       </c>
       <c r="E33">
-        <v>-300.0170000000001</v>
+        <v>-284.724</v>
       </c>
       <c r="F33">
-        <v>474.083</v>
+        <v>489.3760000000001</v>
       </c>
       <c r="G33">
         <v>35</v>
@@ -3987,28 +3987,28 @@
         <v>66.5</v>
       </c>
       <c r="M33">
-        <v>42.66747</v>
+        <v>44.04384</v>
       </c>
       <c r="N33">
-        <v>23.83253</v>
+        <v>22.45616</v>
       </c>
       <c r="O33">
-        <v>4.766506</v>
+        <v>4.491231999999999</v>
       </c>
       <c r="P33">
-        <v>19.066024</v>
+        <v>17.964928</v>
       </c>
       <c r="Q33">
-        <v>63.866024</v>
+        <v>62.764928</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08722414170549113</v>
+        <v>0.08774369697584722</v>
       </c>
       <c r="T33">
-        <v>0.7858006609857978</v>
+        <v>0.7956564324769028</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.558564405154559</v>
+        <v>1.509859267493479</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08270571394357609</v>
+        <v>0.09909989670277566</v>
       </c>
       <c r="C34">
-        <v>679.6728098986877</v>
+        <v>315.5648102935634</v>
       </c>
       <c r="D34">
-        <v>1134.048809898688</v>
+        <v>785.2338102935635</v>
       </c>
       <c r="E34">
-        <v>-284.724</v>
+        <v>-269.431</v>
       </c>
       <c r="F34">
-        <v>489.3760000000001</v>
+        <v>504.6690000000001</v>
       </c>
       <c r="G34">
         <v>35</v>
@@ -4069,45 +4069,45 @@
         <v>66.5</v>
       </c>
       <c r="M34">
-        <v>44.04384</v>
+        <v>74.08540920000002</v>
       </c>
       <c r="N34">
-        <v>22.45616</v>
+        <v>-7.585409200000015</v>
       </c>
       <c r="O34">
-        <v>4.491231999999999</v>
+        <v>-1.517081840000003</v>
       </c>
       <c r="P34">
-        <v>17.964928</v>
+        <v>-6.068327360000012</v>
       </c>
       <c r="Q34">
-        <v>62.764928</v>
+        <v>38.73167263999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08774369697584722</v>
+        <v>0.08858609863214642</v>
       </c>
       <c r="T34">
-        <v>0.7956564324769028</v>
+        <v>0.8116364806102282</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2</v>
+        <v>0.1795225287086624</v>
       </c>
       <c r="W34">
-        <v>0.07199999999999999</v>
+        <v>0.1204460927855684</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.509859267493479</v>
+        <v>0.8976126435433117</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09909989670277566</v>
+        <v>0.1001098967027757</v>
       </c>
       <c r="C35">
-        <v>315.5648102935634</v>
+        <v>285.66883373596</v>
       </c>
       <c r="D35">
-        <v>785.2338102935635</v>
+        <v>770.6308337359601</v>
       </c>
       <c r="E35">
-        <v>-269.431</v>
+        <v>-254.138</v>
       </c>
       <c r="F35">
-        <v>504.6690000000001</v>
+        <v>519.9620000000001</v>
       </c>
       <c r="G35">
         <v>35</v>
@@ -4151,37 +4151,37 @@
         <v>66.5</v>
       </c>
       <c r="M35">
-        <v>74.08540920000002</v>
+        <v>76.33042160000002</v>
       </c>
       <c r="N35">
-        <v>-7.585409200000015</v>
+        <v>-9.830421600000022</v>
       </c>
       <c r="O35">
-        <v>-1.517081840000003</v>
+        <v>-1.966084320000005</v>
       </c>
       <c r="P35">
-        <v>-6.068327360000012</v>
+        <v>-7.864337280000018</v>
       </c>
       <c r="Q35">
-        <v>38.73167263999999</v>
+        <v>36.93566271999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08858609863214642</v>
+        <v>0.08923437285384561</v>
       </c>
       <c r="T35">
-        <v>0.8116364806102282</v>
+        <v>0.8239340030437166</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1795225287086624</v>
+        <v>0.1742424543348782</v>
       </c>
       <c r="W35">
-        <v>0.1204460927855684</v>
+        <v>0.1212212077036399</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8976126435433117</v>
+        <v>0.8712122716743906</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1001098967027757</v>
+        <v>0.1011198967027757</v>
       </c>
       <c r="C36">
-        <v>285.66883373596</v>
+        <v>256.3060832760993</v>
       </c>
       <c r="D36">
-        <v>770.6308337359601</v>
+        <v>756.5610832760995</v>
       </c>
       <c r="E36">
-        <v>-254.138</v>
+        <v>-238.845</v>
       </c>
       <c r="F36">
-        <v>519.9620000000001</v>
+        <v>535.2550000000001</v>
       </c>
       <c r="G36">
         <v>35</v>
@@ -4233,37 +4233,37 @@
         <v>66.5</v>
       </c>
       <c r="M36">
-        <v>76.33042160000002</v>
+        <v>78.57543400000003</v>
       </c>
       <c r="N36">
-        <v>-9.830421600000022</v>
+        <v>-12.07543400000003</v>
       </c>
       <c r="O36">
-        <v>-1.966084320000005</v>
+        <v>-2.415086800000006</v>
       </c>
       <c r="P36">
-        <v>-7.864337280000018</v>
+        <v>-9.660347200000023</v>
       </c>
       <c r="Q36">
-        <v>36.93566271999998</v>
+        <v>35.13965279999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08923437285384561</v>
+        <v>0.08990259397467401</v>
       </c>
       <c r="T36">
-        <v>0.8239340030437166</v>
+        <v>0.8366099107828507</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1742424543348782</v>
+        <v>0.1692640984967388</v>
       </c>
       <c r="W36">
-        <v>0.1212212077036399</v>
+        <v>0.1219520303406788</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8712122716743906</v>
+        <v>0.8463204924836938</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1011198967027757</v>
+        <v>0.1021298967027757</v>
       </c>
       <c r="C37">
-        <v>256.3060832760993</v>
+        <v>227.4478765415516</v>
       </c>
       <c r="D37">
-        <v>756.5610832760995</v>
+        <v>742.9958765415518</v>
       </c>
       <c r="E37">
-        <v>-238.845</v>
+        <v>-223.552</v>
       </c>
       <c r="F37">
-        <v>535.2550000000001</v>
+        <v>550.5480000000001</v>
       </c>
       <c r="G37">
         <v>35</v>
@@ -4315,37 +4315,37 @@
         <v>66.5</v>
       </c>
       <c r="M37">
-        <v>78.57543400000003</v>
+        <v>80.82044640000002</v>
       </c>
       <c r="N37">
-        <v>-12.07543400000003</v>
+        <v>-14.32044640000002</v>
       </c>
       <c r="O37">
-        <v>-2.415086800000006</v>
+        <v>-2.864089280000005</v>
       </c>
       <c r="P37">
-        <v>-9.660347200000023</v>
+        <v>-11.45635712000002</v>
       </c>
       <c r="Q37">
-        <v>35.13965279999997</v>
+        <v>33.34364287999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08990259397467401</v>
+        <v>0.09059169700552828</v>
       </c>
       <c r="T37">
-        <v>0.8366099107828507</v>
+        <v>0.8496819406388327</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1692640984967388</v>
+        <v>0.1645623179829405</v>
       </c>
       <c r="W37">
-        <v>0.1219520303406788</v>
+        <v>0.1226422517201043</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8463204924836938</v>
+        <v>0.8228115899147024</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1021298967027757</v>
+        <v>0.1031398967027757</v>
       </c>
       <c r="C38">
-        <v>227.4478765415521</v>
+        <v>199.0675520352515</v>
       </c>
       <c r="D38">
-        <v>742.9958765415521</v>
+        <v>729.9085520352515</v>
       </c>
       <c r="E38">
-        <v>-223.5520000000001</v>
+        <v>-208.2590000000001</v>
       </c>
       <c r="F38">
-        <v>550.548</v>
+        <v>565.841</v>
       </c>
       <c r="G38">
         <v>35</v>
@@ -4397,37 +4397,37 @@
         <v>66.5</v>
       </c>
       <c r="M38">
-        <v>80.82044640000001</v>
+        <v>83.06545880000002</v>
       </c>
       <c r="N38">
-        <v>-14.32044640000001</v>
+        <v>-16.56545880000002</v>
       </c>
       <c r="O38">
-        <v>-2.864089280000002</v>
+        <v>-3.313091760000003</v>
       </c>
       <c r="P38">
-        <v>-11.45635712000001</v>
+        <v>-13.25236704000001</v>
       </c>
       <c r="Q38">
-        <v>33.34364287999999</v>
+        <v>31.54763295999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09059169700552827</v>
+        <v>0.09130267632307634</v>
       </c>
       <c r="T38">
-        <v>0.8496819406388326</v>
+        <v>0.8631689555696078</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1645623179829405</v>
+        <v>0.1601146877671853</v>
       </c>
       <c r="W38">
-        <v>0.1226422517201043</v>
+        <v>0.1232951638357772</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8228115899147025</v>
+        <v>0.8005734388359267</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1031398967027757</v>
+        <v>0.1251553670625053</v>
       </c>
       <c r="C39">
-        <v>199.0675520352515</v>
+        <v>-18.7231577918368</v>
       </c>
       <c r="D39">
-        <v>729.9085520352515</v>
+        <v>527.4108422081633</v>
       </c>
       <c r="E39">
-        <v>-208.2590000000001</v>
+        <v>-192.966</v>
       </c>
       <c r="F39">
-        <v>565.841</v>
+        <v>581.1340000000001</v>
       </c>
       <c r="G39">
         <v>35</v>
@@ -4479,45 +4479,45 @@
         <v>66.5</v>
       </c>
       <c r="M39">
-        <v>83.06545880000002</v>
+        <v>116.6917072</v>
       </c>
       <c r="N39">
-        <v>-16.56545880000002</v>
+        <v>-50.19170720000002</v>
       </c>
       <c r="O39">
-        <v>-3.313091760000003</v>
+        <v>-10.03834144000001</v>
       </c>
       <c r="P39">
-        <v>-13.25236704000001</v>
+        <v>-40.15336576000002</v>
       </c>
       <c r="Q39">
-        <v>31.54763295999998</v>
+        <v>4.646634239999976</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09130267632307634</v>
+        <v>0.09281960716656093</v>
       </c>
       <c r="T39">
-        <v>0.8631689555696078</v>
+        <v>0.8919445731298845</v>
       </c>
       <c r="U39">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1601146877671853</v>
+        <v>0.1139755370722693</v>
       </c>
       <c r="W39">
-        <v>0.1232951638357772</v>
+        <v>0.1779137121558883</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8005734388359267</v>
+        <v>0.5698776853613466</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1251553670625053</v>
+        <v>0.1267053670625053</v>
       </c>
       <c r="C40">
-        <v>-18.7231577918368</v>
+        <v>-44.12039234516499</v>
       </c>
       <c r="D40">
-        <v>527.4108422081633</v>
+        <v>517.3066076548351</v>
       </c>
       <c r="E40">
-        <v>-192.966</v>
+        <v>-177.673</v>
       </c>
       <c r="F40">
-        <v>581.1340000000001</v>
+        <v>596.4270000000001</v>
       </c>
       <c r="G40">
         <v>35</v>
@@ -4561,37 +4561,37 @@
         <v>66.5</v>
       </c>
       <c r="M40">
-        <v>116.6917072</v>
+        <v>119.7625416</v>
       </c>
       <c r="N40">
-        <v>-50.19170720000002</v>
+        <v>-53.26254160000003</v>
       </c>
       <c r="O40">
-        <v>-10.03834144000001</v>
+        <v>-10.65250832000001</v>
       </c>
       <c r="P40">
-        <v>-40.15336576000002</v>
+        <v>-42.61003328000002</v>
       </c>
       <c r="Q40">
-        <v>4.646634239999976</v>
+        <v>2.189966719999973</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09281960716656093</v>
+        <v>0.09359042039879964</v>
       </c>
       <c r="T40">
-        <v>0.8919445731298845</v>
+        <v>0.9065666153123417</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1139755370722693</v>
+        <v>0.1110530874037496</v>
       </c>
       <c r="W40">
-        <v>0.1779137121558883</v>
+        <v>0.1785005400493271</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5698776853613466</v>
+        <v>0.555265437018748</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1267053670625053</v>
+        <v>0.1282553670625053</v>
       </c>
       <c r="C41">
-        <v>-44.12039234516499</v>
+        <v>-69.13774711345036</v>
       </c>
       <c r="D41">
-        <v>517.3066076548351</v>
+        <v>507.5822528865498</v>
       </c>
       <c r="E41">
-        <v>-177.673</v>
+        <v>-162.38</v>
       </c>
       <c r="F41">
-        <v>596.4270000000001</v>
+        <v>611.7200000000001</v>
       </c>
       <c r="G41">
         <v>35</v>
@@ -4643,37 +4643,37 @@
         <v>66.5</v>
       </c>
       <c r="M41">
-        <v>119.7625416</v>
+        <v>122.833376</v>
       </c>
       <c r="N41">
-        <v>-53.26254160000003</v>
+        <v>-56.33337600000003</v>
       </c>
       <c r="O41">
-        <v>-10.65250832000001</v>
+        <v>-11.26667520000001</v>
       </c>
       <c r="P41">
-        <v>-42.61003328000002</v>
+        <v>-45.06670080000002</v>
       </c>
       <c r="Q41">
-        <v>2.189966719999973</v>
+        <v>-0.2667008000000237</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09359042039879964</v>
+        <v>0.0943869274054463</v>
       </c>
       <c r="T41">
-        <v>0.9065666153123417</v>
+        <v>0.9216760589008808</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1110530874037496</v>
+        <v>0.1082767602186559</v>
       </c>
       <c r="W41">
-        <v>0.1785005400493271</v>
+        <v>0.1790580265480939</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.555265437018748</v>
+        <v>0.5413838010932792</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1282553670625053</v>
+        <v>0.1298053670625053</v>
       </c>
       <c r="C42">
-        <v>-69.13774711345036</v>
+        <v>-93.7962498126858</v>
       </c>
       <c r="D42">
-        <v>507.5822528865498</v>
+        <v>498.2167501873143</v>
       </c>
       <c r="E42">
-        <v>-162.38</v>
+        <v>-147.087</v>
       </c>
       <c r="F42">
-        <v>611.7200000000001</v>
+        <v>627.0130000000001</v>
       </c>
       <c r="G42">
         <v>35</v>
@@ -4725,37 +4725,37 @@
         <v>66.5</v>
       </c>
       <c r="M42">
-        <v>122.833376</v>
+        <v>125.9042104</v>
       </c>
       <c r="N42">
-        <v>-56.33337600000003</v>
+        <v>-59.40421040000004</v>
       </c>
       <c r="O42">
-        <v>-11.26667520000001</v>
+        <v>-11.88084208000001</v>
       </c>
       <c r="P42">
-        <v>-45.06670080000002</v>
+        <v>-47.52336832000003</v>
       </c>
       <c r="Q42">
-        <v>-0.2667008000000237</v>
+        <v>-2.723368320000034</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0943869274054463</v>
+        <v>0.09521043464960639</v>
       </c>
       <c r="T42">
-        <v>0.9216760589008808</v>
+        <v>0.9372976870178448</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1082767602186559</v>
+        <v>0.1056358636279569</v>
       </c>
       <c r="W42">
-        <v>0.1790580265480939</v>
+        <v>0.1795883185835062</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5413838010932792</v>
+        <v>0.5281793181397847</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1298053670625053</v>
+        <v>0.1313553670625053</v>
       </c>
       <c r="C43">
-        <v>-93.7962498126858</v>
+        <v>-118.1154043288151</v>
       </c>
       <c r="D43">
-        <v>498.2167501873143</v>
+        <v>489.1905956711851</v>
       </c>
       <c r="E43">
-        <v>-147.087</v>
+        <v>-131.794</v>
       </c>
       <c r="F43">
-        <v>627.0130000000001</v>
+        <v>642.3060000000002</v>
       </c>
       <c r="G43">
         <v>35</v>
@@ -4807,37 +4807,37 @@
         <v>66.5</v>
       </c>
       <c r="M43">
-        <v>125.9042104</v>
+        <v>128.9750448</v>
       </c>
       <c r="N43">
-        <v>-59.40421040000004</v>
+        <v>-62.47504480000003</v>
       </c>
       <c r="O43">
-        <v>-11.88084208000001</v>
+        <v>-12.49500896000001</v>
       </c>
       <c r="P43">
-        <v>-47.52336832000003</v>
+        <v>-49.98003584000003</v>
       </c>
       <c r="Q43">
-        <v>-2.723368320000034</v>
+        <v>-5.180035840000031</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09521043464960639</v>
+        <v>0.09606233869528927</v>
       </c>
       <c r="T43">
-        <v>0.9372976870178448</v>
+        <v>0.9534579919664283</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1056358636279569</v>
+        <v>0.1031207240177675</v>
       </c>
       <c r="W43">
-        <v>0.1795883185835062</v>
+        <v>0.1800933586172323</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5281793181397847</v>
+        <v>0.5156036200888374</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1313553670625053</v>
+        <v>0.1329053670625053</v>
       </c>
       <c r="C44">
-        <v>-118.115404328815</v>
+        <v>-142.1133262970128</v>
       </c>
       <c r="D44">
-        <v>489.1905956711851</v>
+        <v>480.4856737029873</v>
       </c>
       <c r="E44">
-        <v>-131.7940000000001</v>
+        <v>-116.5010000000001</v>
       </c>
       <c r="F44">
-        <v>642.306</v>
+        <v>657.599</v>
       </c>
       <c r="G44">
         <v>35</v>
@@ -4889,37 +4889,37 @@
         <v>66.5</v>
       </c>
       <c r="M44">
-        <v>128.9750448</v>
+        <v>132.0458792</v>
       </c>
       <c r="N44">
-        <v>-62.47504480000001</v>
+        <v>-65.5458792</v>
       </c>
       <c r="O44">
-        <v>-12.49500896</v>
+        <v>-13.10917584</v>
       </c>
       <c r="P44">
-        <v>-49.98003584000001</v>
+        <v>-52.43670336</v>
       </c>
       <c r="Q44">
-        <v>-5.180035840000009</v>
+        <v>-7.636703360000006</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09606233869528927</v>
+        <v>0.09694413411099609</v>
       </c>
       <c r="T44">
-        <v>0.9534579919664283</v>
+        <v>0.9701853251588216</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1031207240177675</v>
+        <v>0.1007225676452613</v>
       </c>
       <c r="W44">
-        <v>0.1800933586172323</v>
+        <v>0.1805749084168315</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5156036200888374</v>
+        <v>0.5036128382263064</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1329053670625053</v>
+        <v>0.1500512602164879</v>
       </c>
       <c r="C45">
-        <v>-142.1133262970128</v>
+        <v>-236.4303688478944</v>
       </c>
       <c r="D45">
-        <v>480.4856737029873</v>
+        <v>401.4616311521056</v>
       </c>
       <c r="E45">
-        <v>-116.5010000000001</v>
+        <v>-101.2080000000001</v>
       </c>
       <c r="F45">
-        <v>657.599</v>
+        <v>672.8920000000001</v>
       </c>
       <c r="G45">
         <v>35</v>
@@ -4971,45 +4971,45 @@
         <v>66.5</v>
       </c>
       <c r="M45">
-        <v>132.0458792</v>
+        <v>158.6679336</v>
       </c>
       <c r="N45">
-        <v>-65.5458792</v>
+        <v>-92.16793360000003</v>
       </c>
       <c r="O45">
-        <v>-13.10917584</v>
+        <v>-18.43358672</v>
       </c>
       <c r="P45">
-        <v>-52.43670336</v>
+        <v>-73.73434688000002</v>
       </c>
       <c r="Q45">
-        <v>-7.636703360000006</v>
+        <v>-28.93434688000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09694413411099609</v>
+        <v>0.09820723142366136</v>
       </c>
       <c r="T45">
-        <v>0.9701853251588216</v>
+        <v>0.9941458144367488</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1007225676452613</v>
+        <v>0.08382286009679274</v>
       </c>
       <c r="W45">
-        <v>0.1805749084168315</v>
+        <v>0.2160345695891763</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5036128382263064</v>
+        <v>0.4191143004839636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1500512602164879</v>
+        <v>0.1519512602164879</v>
       </c>
       <c r="C46">
-        <v>-236.4303688478944</v>
+        <v>-258.9091252641007</v>
       </c>
       <c r="D46">
-        <v>401.4616311521056</v>
+        <v>394.2758747358994</v>
       </c>
       <c r="E46">
-        <v>-101.2080000000001</v>
+        <v>-85.91500000000008</v>
       </c>
       <c r="F46">
-        <v>672.8920000000001</v>
+        <v>688.1850000000001</v>
       </c>
       <c r="G46">
         <v>35</v>
@@ -5053,37 +5053,37 @@
         <v>66.5</v>
       </c>
       <c r="M46">
-        <v>158.6679336</v>
+        <v>162.274023</v>
       </c>
       <c r="N46">
-        <v>-92.16793360000003</v>
+        <v>-95.77402300000003</v>
       </c>
       <c r="O46">
-        <v>-18.43358672</v>
+        <v>-19.15480460000001</v>
       </c>
       <c r="P46">
-        <v>-73.73434688000002</v>
+        <v>-76.61921840000002</v>
       </c>
       <c r="Q46">
-        <v>-28.93434688000002</v>
+        <v>-31.81921840000003</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09820723142366136</v>
+        <v>0.09916009017681883</v>
       </c>
       <c r="T46">
-        <v>0.9941458144367488</v>
+        <v>1.012221192881053</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08382286009679274</v>
+        <v>0.08196012987241956</v>
       </c>
       <c r="W46">
-        <v>0.2160345695891763</v>
+        <v>0.2164738013760835</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4191143004839636</v>
+        <v>0.4098006493620978</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1519512602164879</v>
+        <v>0.1538512602164879</v>
       </c>
       <c r="C47">
-        <v>-258.9091252641007</v>
+        <v>-281.1351694553231</v>
       </c>
       <c r="D47">
-        <v>394.2758747358994</v>
+        <v>387.3428305446769</v>
       </c>
       <c r="E47">
-        <v>-85.91500000000008</v>
+        <v>-70.62200000000007</v>
       </c>
       <c r="F47">
-        <v>688.1850000000001</v>
+        <v>703.4780000000001</v>
       </c>
       <c r="G47">
         <v>35</v>
@@ -5135,37 +5135,37 @@
         <v>66.5</v>
       </c>
       <c r="M47">
-        <v>162.274023</v>
+        <v>165.8801124</v>
       </c>
       <c r="N47">
-        <v>-95.77402300000003</v>
+        <v>-99.38011240000003</v>
       </c>
       <c r="O47">
-        <v>-19.15480460000001</v>
+        <v>-19.87602248000001</v>
       </c>
       <c r="P47">
-        <v>-76.61921840000002</v>
+        <v>-79.50408992000003</v>
       </c>
       <c r="Q47">
-        <v>-31.81921840000003</v>
+        <v>-34.70408992000003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09916009017681883</v>
+        <v>0.1001482399949081</v>
       </c>
       <c r="T47">
-        <v>1.012221192881053</v>
+        <v>1.030966029786258</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08196012987241956</v>
+        <v>0.08017838791867131</v>
       </c>
       <c r="W47">
-        <v>0.2164738013760835</v>
+        <v>0.2168939361287773</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4098006493620978</v>
+        <v>0.4008919395933566</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1538512602164879</v>
+        <v>0.1557512602164879</v>
       </c>
       <c r="C48">
-        <v>-281.1351694553231</v>
+        <v>-303.1216023144451</v>
       </c>
       <c r="D48">
-        <v>387.3428305446769</v>
+        <v>380.6493976855551</v>
       </c>
       <c r="E48">
-        <v>-70.62200000000007</v>
+        <v>-55.32899999999995</v>
       </c>
       <c r="F48">
-        <v>703.4780000000001</v>
+        <v>718.7710000000002</v>
       </c>
       <c r="G48">
         <v>35</v>
@@ -5217,37 +5217,37 @@
         <v>66.5</v>
       </c>
       <c r="M48">
-        <v>165.8801124</v>
+        <v>169.4862018000001</v>
       </c>
       <c r="N48">
-        <v>-99.38011240000003</v>
+        <v>-102.9862018000001</v>
       </c>
       <c r="O48">
-        <v>-19.87602248000001</v>
+        <v>-20.59724036000001</v>
       </c>
       <c r="P48">
-        <v>-79.50408992000003</v>
+        <v>-82.38896144000005</v>
       </c>
       <c r="Q48">
-        <v>-34.70408992000003</v>
+        <v>-37.58896144000005</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1001482399949081</v>
+        <v>0.101173678485378</v>
       </c>
       <c r="T48">
-        <v>1.030966029786258</v>
+        <v>1.050418219027508</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08017838791867131</v>
+        <v>0.07847246477146552</v>
       </c>
       <c r="W48">
-        <v>0.2168939361287773</v>
+        <v>0.2172961928068884</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4008919395933566</v>
+        <v>0.3923623238573276</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1557512602164879</v>
+        <v>0.157651260216488</v>
       </c>
       <c r="C49">
-        <v>-303.1216023144451</v>
+        <v>-324.880634563011</v>
       </c>
       <c r="D49">
-        <v>380.6493976855551</v>
+        <v>374.1833654369892</v>
       </c>
       <c r="E49">
-        <v>-55.32899999999995</v>
+        <v>-40.03599999999994</v>
       </c>
       <c r="F49">
-        <v>718.7710000000002</v>
+        <v>734.0640000000002</v>
       </c>
       <c r="G49">
         <v>35</v>
@@ -5299,37 +5299,37 @@
         <v>66.5</v>
       </c>
       <c r="M49">
-        <v>169.4862018000001</v>
+        <v>173.0922912000001</v>
       </c>
       <c r="N49">
-        <v>-102.9862018000001</v>
+        <v>-106.5922912000001</v>
       </c>
       <c r="O49">
-        <v>-20.59724036000001</v>
+        <v>-21.31845824000001</v>
       </c>
       <c r="P49">
-        <v>-82.38896144000005</v>
+        <v>-85.27383296000005</v>
       </c>
       <c r="Q49">
-        <v>-37.58896144000005</v>
+        <v>-40.47383296000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.101173678485378</v>
+        <v>0.1022385569177892</v>
       </c>
       <c r="T49">
-        <v>1.050418219027508</v>
+        <v>1.070618569393422</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07847246477146552</v>
+        <v>0.07683762175539333</v>
       </c>
       <c r="W49">
-        <v>0.2172961928068884</v>
+        <v>0.2176816887900783</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3923623238573276</v>
+        <v>0.3841881087769666</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1576512602164879</v>
+        <v>0.1595512602164879</v>
       </c>
       <c r="C50">
-        <v>-324.8806345630109</v>
+        <v>-346.4236610943848</v>
       </c>
       <c r="D50">
-        <v>374.1833654369892</v>
+        <v>367.9333389056152</v>
       </c>
       <c r="E50">
-        <v>-40.03600000000006</v>
+        <v>-24.74300000000005</v>
       </c>
       <c r="F50">
-        <v>734.0640000000001</v>
+        <v>749.3570000000001</v>
       </c>
       <c r="G50">
         <v>35</v>
@@ -5381,37 +5381,37 @@
         <v>66.5</v>
       </c>
       <c r="M50">
-        <v>173.0922912</v>
+        <v>176.6983806</v>
       </c>
       <c r="N50">
-        <v>-106.5922912</v>
+        <v>-110.1983806</v>
       </c>
       <c r="O50">
-        <v>-21.31845824000001</v>
+        <v>-22.03967612000001</v>
       </c>
       <c r="P50">
-        <v>-85.27383296000002</v>
+        <v>-88.15870448000003</v>
       </c>
       <c r="Q50">
-        <v>-40.47383296000002</v>
+        <v>-43.35870448000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1022385569177891</v>
+        <v>0.1033451952887262</v>
       </c>
       <c r="T50">
-        <v>1.070618569393422</v>
+        <v>1.09161109036192</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07683762175539333</v>
+        <v>0.07526950702569143</v>
       </c>
       <c r="W50">
-        <v>0.2176816887900783</v>
+        <v>0.218051450243342</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3841881087769666</v>
+        <v>0.3763475351284571</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1595512602164879</v>
+        <v>0.1614512602164879</v>
       </c>
       <c r="C51">
-        <v>-346.4236610943848</v>
+        <v>-367.7613279887367</v>
       </c>
       <c r="D51">
-        <v>367.9333389056152</v>
+        <v>361.8886720112634</v>
       </c>
       <c r="E51">
-        <v>-24.74300000000005</v>
+        <v>-9.450000000000045</v>
       </c>
       <c r="F51">
-        <v>749.3570000000001</v>
+        <v>764.6500000000001</v>
       </c>
       <c r="G51">
         <v>35</v>
@@ -5463,37 +5463,37 @@
         <v>66.5</v>
       </c>
       <c r="M51">
-        <v>176.6983806</v>
+        <v>180.30447</v>
       </c>
       <c r="N51">
-        <v>-110.1983806</v>
+        <v>-113.80447</v>
       </c>
       <c r="O51">
-        <v>-22.03967612000001</v>
+        <v>-22.76089400000001</v>
       </c>
       <c r="P51">
-        <v>-88.15870448000003</v>
+        <v>-91.04357600000003</v>
       </c>
       <c r="Q51">
-        <v>-43.35870448000003</v>
+        <v>-46.24357600000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1033451952887262</v>
+        <v>0.1044960991945007</v>
       </c>
       <c r="T51">
-        <v>1.09161109036192</v>
+        <v>1.113443312169158</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07526950702569143</v>
+        <v>0.0737641168851776</v>
       </c>
       <c r="W51">
-        <v>0.218051450243342</v>
+        <v>0.2184064212384751</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3763475351284571</v>
+        <v>0.3688205844258879</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1614512602164879</v>
+        <v>0.1633512602164879</v>
       </c>
       <c r="C52">
-        <v>-367.7613279887367</v>
+        <v>-388.9035930289847</v>
       </c>
       <c r="D52">
-        <v>361.8886720112634</v>
+        <v>356.0394069710154</v>
       </c>
       <c r="E52">
-        <v>-9.450000000000045</v>
+        <v>5.842999999999961</v>
       </c>
       <c r="F52">
-        <v>764.6500000000001</v>
+        <v>779.9430000000001</v>
       </c>
       <c r="G52">
         <v>35</v>
@@ -5545,37 +5545,37 @@
         <v>66.5</v>
       </c>
       <c r="M52">
-        <v>180.30447</v>
+        <v>183.9105594</v>
       </c>
       <c r="N52">
-        <v>-113.80447</v>
+        <v>-117.4105594</v>
       </c>
       <c r="O52">
-        <v>-22.76089400000001</v>
+        <v>-23.48211188000001</v>
       </c>
       <c r="P52">
-        <v>-91.04357600000003</v>
+        <v>-93.92844752000003</v>
       </c>
       <c r="Q52">
-        <v>-46.24357600000003</v>
+        <v>-49.12844752000004</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1044960991945007</v>
+        <v>0.1056939787698987</v>
       </c>
       <c r="T52">
-        <v>1.113443312169158</v>
+        <v>1.13616664507057</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0737641168851776</v>
+        <v>0.0723177616521349</v>
       </c>
       <c r="W52">
-        <v>0.2184064212384751</v>
+        <v>0.2187474718024266</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3688205844258879</v>
+        <v>0.3615888082606745</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1633512602164879</v>
+        <v>0.1652512602164879</v>
       </c>
       <c r="C53">
-        <v>-388.9035930289847</v>
+        <v>-409.8597804413145</v>
       </c>
       <c r="D53">
-        <v>356.0394069710154</v>
+        <v>350.3762195586856</v>
       </c>
       <c r="E53">
-        <v>5.842999999999961</v>
+        <v>21.13599999999997</v>
       </c>
       <c r="F53">
-        <v>779.9430000000001</v>
+        <v>795.2360000000001</v>
       </c>
       <c r="G53">
         <v>35</v>
@@ -5627,37 +5627,37 @@
         <v>66.5</v>
       </c>
       <c r="M53">
-        <v>183.9105594</v>
+        <v>187.5166488</v>
       </c>
       <c r="N53">
-        <v>-117.4105594</v>
+        <v>-121.0166488</v>
       </c>
       <c r="O53">
-        <v>-23.48211188000001</v>
+        <v>-24.20332976000001</v>
       </c>
       <c r="P53">
-        <v>-93.92844752000003</v>
+        <v>-96.81331904000004</v>
       </c>
       <c r="Q53">
-        <v>-49.12844752000004</v>
+        <v>-52.01331904000004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1056939787698987</v>
+        <v>0.1069417699942716</v>
       </c>
       <c r="T53">
-        <v>1.13616664507057</v>
+        <v>1.15983678350954</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0723177616521349</v>
+        <v>0.07092703546651692</v>
       </c>
       <c r="W53">
-        <v>0.2187474718024266</v>
+        <v>0.2190754050369953</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3615888082606745</v>
+        <v>0.3546351773325845</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1652512602164879</v>
+        <v>0.1671512602164879</v>
       </c>
       <c r="C54">
-        <v>-409.8597804413145</v>
+        <v>-430.6386304932537</v>
       </c>
       <c r="D54">
-        <v>350.3762195586856</v>
+        <v>344.8903695067464</v>
       </c>
       <c r="E54">
-        <v>21.13599999999997</v>
+        <v>36.42899999999997</v>
       </c>
       <c r="F54">
-        <v>795.2360000000001</v>
+        <v>810.5290000000001</v>
       </c>
       <c r="G54">
         <v>35</v>
@@ -5709,37 +5709,37 @@
         <v>66.5</v>
       </c>
       <c r="M54">
-        <v>187.5166488</v>
+        <v>191.1227382</v>
       </c>
       <c r="N54">
-        <v>-121.0166488</v>
+        <v>-124.6227382</v>
       </c>
       <c r="O54">
-        <v>-24.20332976000001</v>
+        <v>-24.92454764000001</v>
       </c>
       <c r="P54">
-        <v>-96.81331904000004</v>
+        <v>-99.69819056000003</v>
       </c>
       <c r="Q54">
-        <v>-52.01331904000004</v>
+        <v>-54.89819056000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1069417699942716</v>
+        <v>0.108242658717554</v>
       </c>
       <c r="T54">
-        <v>1.15983678350954</v>
+        <v>1.184514161882084</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07092703546651692</v>
+        <v>0.06958878951431849</v>
       </c>
       <c r="W54">
-        <v>0.2190754050369953</v>
+        <v>0.2193909634325237</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3546351773325845</v>
+        <v>0.3479439475715924</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1671512602164879</v>
+        <v>0.1690512602164879</v>
       </c>
       <c r="C55">
-        <v>-430.6386304932537</v>
+        <v>-451.2483445042246</v>
       </c>
       <c r="D55">
-        <v>344.8903695067464</v>
+        <v>339.5736554957755</v>
       </c>
       <c r="E55">
-        <v>36.42899999999997</v>
+        <v>51.72199999999998</v>
       </c>
       <c r="F55">
-        <v>810.5290000000001</v>
+        <v>825.8220000000001</v>
       </c>
       <c r="G55">
         <v>35</v>
@@ -5791,37 +5791,37 @@
         <v>66.5</v>
       </c>
       <c r="M55">
-        <v>191.1227382</v>
+        <v>194.7288276</v>
       </c>
       <c r="N55">
-        <v>-124.6227382</v>
+        <v>-128.2288276</v>
       </c>
       <c r="O55">
-        <v>-24.92454764000001</v>
+        <v>-25.64576552000001</v>
       </c>
       <c r="P55">
-        <v>-99.69819056000003</v>
+        <v>-102.58306208</v>
       </c>
       <c r="Q55">
-        <v>-54.89819056000003</v>
+        <v>-57.78306208000004</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.108242658717554</v>
+        <v>0.1096001078201095</v>
       </c>
       <c r="T55">
-        <v>1.184514161882084</v>
+        <v>1.210264469749085</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06958878951431849</v>
+        <v>0.06830010822701629</v>
       </c>
       <c r="W55">
-        <v>0.2193909634325237</v>
+        <v>0.2196948344800696</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3479439475715924</v>
+        <v>0.3415005411350814</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1690512602164879</v>
+        <v>0.1709512602164879</v>
       </c>
       <c r="C56">
-        <v>-451.2483445042246</v>
+        <v>-471.6966257560946</v>
       </c>
       <c r="D56">
-        <v>339.5736554957755</v>
+        <v>334.4183742439055</v>
       </c>
       <c r="E56">
-        <v>51.72199999999998</v>
+        <v>67.01499999999999</v>
       </c>
       <c r="F56">
-        <v>825.8220000000001</v>
+        <v>841.1150000000001</v>
       </c>
       <c r="G56">
         <v>35</v>
@@ -5873,37 +5873,37 @@
         <v>66.5</v>
       </c>
       <c r="M56">
-        <v>194.7288276</v>
+        <v>198.334917</v>
       </c>
       <c r="N56">
-        <v>-128.2288276</v>
+        <v>-131.834917</v>
       </c>
       <c r="O56">
-        <v>-25.64576552000001</v>
+        <v>-26.36698340000001</v>
       </c>
       <c r="P56">
-        <v>-102.58306208</v>
+        <v>-105.4679336</v>
       </c>
       <c r="Q56">
-        <v>-57.78306208000004</v>
+        <v>-60.66793360000004</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1096001078201095</v>
+        <v>0.1110178879938897</v>
       </c>
       <c r="T56">
-        <v>1.210264469749085</v>
+        <v>1.23715923574351</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06830010822701629</v>
+        <v>0.06705828807743418</v>
       </c>
       <c r="W56">
-        <v>0.2196948344800696</v>
+        <v>0.219987655671341</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3415005411350814</v>
+        <v>0.3352914403871708</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1709512602164879</v>
+        <v>0.1728512602164879</v>
       </c>
       <c r="C57">
-        <v>-471.6966257560946</v>
+        <v>-491.9907167329235</v>
       </c>
       <c r="D57">
-        <v>334.4183742439055</v>
+        <v>329.4172832670766</v>
       </c>
       <c r="E57">
-        <v>67.01499999999999</v>
+        <v>82.30799999999999</v>
       </c>
       <c r="F57">
-        <v>841.1150000000001</v>
+        <v>856.4080000000001</v>
       </c>
       <c r="G57">
         <v>35</v>
@@ -5955,37 +5955,37 @@
         <v>66.5</v>
       </c>
       <c r="M57">
-        <v>198.334917</v>
+        <v>201.9410064</v>
       </c>
       <c r="N57">
-        <v>-131.834917</v>
+        <v>-135.4410064</v>
       </c>
       <c r="O57">
-        <v>-26.36698340000001</v>
+        <v>-27.08820128000001</v>
       </c>
       <c r="P57">
-        <v>-105.4679336</v>
+        <v>-108.35280512</v>
       </c>
       <c r="Q57">
-        <v>-60.66793360000004</v>
+        <v>-63.55280512000004</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1110178879938897</v>
+        <v>0.1125001127210235</v>
       </c>
       <c r="T57">
-        <v>1.23715923574351</v>
+        <v>1.265276491101317</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06705828807743418</v>
+        <v>0.06586081864747999</v>
       </c>
       <c r="W57">
-        <v>0.219987655671341</v>
+        <v>0.2202700189629242</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3352914403871708</v>
+        <v>0.3293040932374</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1728512602164879</v>
+        <v>0.1747512602164879</v>
       </c>
       <c r="C58">
-        <v>-491.9907167329235</v>
+        <v>-512.1374330685117</v>
       </c>
       <c r="D58">
-        <v>329.4172832670766</v>
+        <v>324.5635669314885</v>
       </c>
       <c r="E58">
-        <v>82.30799999999999</v>
+        <v>97.60100000000011</v>
       </c>
       <c r="F58">
-        <v>856.4080000000001</v>
+        <v>871.7010000000002</v>
       </c>
       <c r="G58">
         <v>35</v>
@@ -6037,37 +6037,37 @@
         <v>66.5</v>
       </c>
       <c r="M58">
-        <v>201.9410064</v>
+        <v>205.5470958000001</v>
       </c>
       <c r="N58">
-        <v>-135.4410064</v>
+        <v>-139.0470958000001</v>
       </c>
       <c r="O58">
-        <v>-27.08820128000001</v>
+        <v>-27.80941916000002</v>
       </c>
       <c r="P58">
-        <v>-108.35280512</v>
+        <v>-111.2376766400001</v>
       </c>
       <c r="Q58">
-        <v>-63.55280512000004</v>
+        <v>-66.43767664000006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1125001127210235</v>
+        <v>0.1140512781331404</v>
       </c>
       <c r="T58">
-        <v>1.265276491101317</v>
+        <v>1.294701525778091</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06586081864747999</v>
+        <v>0.06470536568875228</v>
       </c>
       <c r="W58">
-        <v>0.2202700189629242</v>
+        <v>0.2205424747705922</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3293040932374</v>
+        <v>0.3235268284437613</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1747512602164879</v>
+        <v>0.1766512602164879</v>
       </c>
       <c r="C59">
-        <v>-512.1374330685117</v>
+        <v>-532.1431945363767</v>
       </c>
       <c r="D59">
-        <v>324.5635669314885</v>
+        <v>319.8508054636236</v>
       </c>
       <c r="E59">
-        <v>97.60100000000011</v>
+        <v>112.8940000000001</v>
       </c>
       <c r="F59">
-        <v>871.7010000000002</v>
+        <v>886.9940000000003</v>
       </c>
       <c r="G59">
         <v>35</v>
@@ -6119,37 +6119,37 @@
         <v>66.5</v>
       </c>
       <c r="M59">
-        <v>205.5470958000001</v>
+        <v>209.1531852000001</v>
       </c>
       <c r="N59">
-        <v>-139.0470958000001</v>
+        <v>-142.6531852000001</v>
       </c>
       <c r="O59">
-        <v>-27.80941916000002</v>
+        <v>-28.53063704000002</v>
       </c>
       <c r="P59">
-        <v>-111.2376766400001</v>
+        <v>-114.1225481600001</v>
       </c>
       <c r="Q59">
-        <v>-66.43767664000006</v>
+        <v>-69.32254816000007</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1140512781331404</v>
+        <v>0.1156763085648818</v>
       </c>
       <c r="T59">
-        <v>1.294701525778091</v>
+        <v>1.325527752582332</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06470536568875228</v>
+        <v>0.06358975593549791</v>
       </c>
       <c r="W59">
-        <v>0.2205424747705922</v>
+        <v>0.2208055355504096</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3235268284437613</v>
+        <v>0.3179487796774896</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1766512602164879</v>
+        <v>0.1785512602164879</v>
       </c>
       <c r="C60">
-        <v>-532.1431945363763</v>
+        <v>-552.0140533784684</v>
       </c>
       <c r="D60">
-        <v>319.8508054636238</v>
+        <v>315.2729466215317</v>
       </c>
       <c r="E60">
-        <v>112.8939999999999</v>
+        <v>128.1869999999999</v>
       </c>
       <c r="F60">
-        <v>886.994</v>
+        <v>902.287</v>
       </c>
       <c r="G60">
         <v>35</v>
@@ -6201,37 +6201,37 @@
         <v>66.5</v>
       </c>
       <c r="M60">
-        <v>209.1531852</v>
+        <v>212.7592746</v>
       </c>
       <c r="N60">
-        <v>-142.6531852</v>
+        <v>-146.2592746</v>
       </c>
       <c r="O60">
-        <v>-28.53063704000001</v>
+        <v>-29.25185492000001</v>
       </c>
       <c r="P60">
-        <v>-114.12254816</v>
+        <v>-117.00741968</v>
       </c>
       <c r="Q60">
-        <v>-69.32254816000003</v>
+        <v>-72.20741968000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1156763085648818</v>
+        <v>0.1173806087737813</v>
       </c>
       <c r="T60">
-        <v>1.325527752582331</v>
+        <v>1.357857697767266</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06358975593549794</v>
+        <v>0.06251196346201492</v>
       </c>
       <c r="W60">
-        <v>0.2208055355504096</v>
+        <v>0.2210596790156569</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3179487796774897</v>
+        <v>0.3125598173100745</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1785512602164879</v>
+        <v>0.1804512602164879</v>
       </c>
       <c r="C61">
-        <v>-552.0140533784684</v>
+        <v>-571.7557202354872</v>
       </c>
       <c r="D61">
-        <v>315.2729466215317</v>
+        <v>310.8242797645129</v>
       </c>
       <c r="E61">
-        <v>128.1869999999999</v>
+        <v>143.4799999999999</v>
       </c>
       <c r="F61">
-        <v>902.287</v>
+        <v>917.58</v>
       </c>
       <c r="G61">
         <v>35</v>
@@ -6283,37 +6283,37 @@
         <v>66.5</v>
       </c>
       <c r="M61">
-        <v>212.7592746</v>
+        <v>216.365364</v>
       </c>
       <c r="N61">
-        <v>-146.2592746</v>
+        <v>-149.865364</v>
       </c>
       <c r="O61">
-        <v>-29.25185492000001</v>
+        <v>-29.97307280000001</v>
       </c>
       <c r="P61">
-        <v>-117.00741968</v>
+        <v>-119.8922912</v>
       </c>
       <c r="Q61">
-        <v>-72.20741968000003</v>
+        <v>-75.09229120000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1173806087737813</v>
+        <v>0.1191701239931259</v>
       </c>
       <c r="T61">
-        <v>1.357857697767266</v>
+        <v>1.391804140211448</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06251196346201492</v>
+        <v>0.06147009740431467</v>
       </c>
       <c r="W61">
-        <v>0.2210596790156569</v>
+        <v>0.2213053510320626</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3125598173100745</v>
+        <v>0.3073504870215733</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1804512602164879</v>
+        <v>0.1823512602164879</v>
       </c>
       <c r="C62">
-        <v>-571.7557202354872</v>
+        <v>-591.3735879124042</v>
       </c>
       <c r="D62">
-        <v>310.8242797645129</v>
+        <v>306.4994120875959</v>
       </c>
       <c r="E62">
-        <v>143.4799999999999</v>
+        <v>158.7729999999999</v>
       </c>
       <c r="F62">
-        <v>917.58</v>
+        <v>932.873</v>
       </c>
       <c r="G62">
         <v>35</v>
@@ -6365,37 +6365,37 @@
         <v>66.5</v>
       </c>
       <c r="M62">
-        <v>216.365364</v>
+        <v>219.9714534</v>
       </c>
       <c r="N62">
-        <v>-149.865364</v>
+        <v>-153.4714534</v>
       </c>
       <c r="O62">
-        <v>-29.97307280000001</v>
+        <v>-30.69429068000001</v>
       </c>
       <c r="P62">
-        <v>-119.8922912</v>
+        <v>-122.77716272</v>
       </c>
       <c r="Q62">
-        <v>-75.09229120000002</v>
+        <v>-77.97716272000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1191701239931259</v>
+        <v>0.1210514092237189</v>
       </c>
       <c r="T62">
-        <v>1.391804140211448</v>
+        <v>1.427491425857896</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06147009740431467</v>
+        <v>0.06046239088948984</v>
       </c>
       <c r="W62">
-        <v>0.2213053510320626</v>
+        <v>0.2215429682282583</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3073504870215733</v>
+        <v>0.3023119544474492</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1823512602164879</v>
+        <v>0.1842512602164879</v>
       </c>
       <c r="C63">
-        <v>-591.3735879124042</v>
+        <v>-610.8727531871432</v>
       </c>
       <c r="D63">
-        <v>306.4994120875959</v>
+        <v>302.2932468128569</v>
       </c>
       <c r="E63">
-        <v>158.7729999999999</v>
+        <v>174.0659999999999</v>
       </c>
       <c r="F63">
-        <v>932.873</v>
+        <v>948.1660000000001</v>
       </c>
       <c r="G63">
         <v>35</v>
@@ -6447,37 +6447,37 @@
         <v>66.5</v>
       </c>
       <c r="M63">
-        <v>219.9714534</v>
+        <v>223.5775428</v>
       </c>
       <c r="N63">
-        <v>-153.4714534</v>
+        <v>-157.0775428</v>
       </c>
       <c r="O63">
-        <v>-30.69429068000001</v>
+        <v>-31.41550856000001</v>
       </c>
       <c r="P63">
-        <v>-122.77716272</v>
+        <v>-125.66203424</v>
       </c>
       <c r="Q63">
-        <v>-77.97716272000002</v>
+        <v>-80.86203424000003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1210514092237189</v>
+        <v>0.1230317094664483</v>
       </c>
       <c r="T63">
-        <v>1.427491425857896</v>
+        <v>1.465056989696262</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06046239088948984</v>
+        <v>0.05948719103643355</v>
       </c>
       <c r="W63">
-        <v>0.2215429682282583</v>
+        <v>0.221772920353609</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3023119544474492</v>
+        <v>0.2974359551821677</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1842512602164879</v>
+        <v>0.1861512602164879</v>
       </c>
       <c r="C64">
-        <v>-610.8727531871432</v>
+        <v>-630.2580368478564</v>
       </c>
       <c r="D64">
-        <v>302.2932468128569</v>
+        <v>298.2009631521438</v>
       </c>
       <c r="E64">
-        <v>174.0659999999999</v>
+        <v>189.359</v>
       </c>
       <c r="F64">
-        <v>948.1660000000001</v>
+        <v>963.4590000000002</v>
       </c>
       <c r="G64">
         <v>35</v>
@@ -6529,37 +6529,37 @@
         <v>66.5</v>
       </c>
       <c r="M64">
-        <v>223.5775428</v>
+        <v>227.1836322000001</v>
       </c>
       <c r="N64">
-        <v>-157.0775428</v>
+        <v>-160.6836322000001</v>
       </c>
       <c r="O64">
-        <v>-31.41550856000001</v>
+        <v>-32.13672644000001</v>
       </c>
       <c r="P64">
-        <v>-125.66203424</v>
+        <v>-128.54690576</v>
       </c>
       <c r="Q64">
-        <v>-80.86203424000003</v>
+        <v>-83.74690576000005</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1230317094664483</v>
+        <v>0.1251190529655415</v>
       </c>
       <c r="T64">
-        <v>1.465056989696262</v>
+        <v>1.504653124552917</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05948719103643355</v>
+        <v>0.0585429499088711</v>
       </c>
       <c r="W64">
-        <v>0.221772920353609</v>
+        <v>0.2219955724114882</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2974359551821677</v>
+        <v>0.2927147495443555</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1861512602164879</v>
+        <v>0.1880512602164879</v>
       </c>
       <c r="C65">
-        <v>-630.2580368478564</v>
+        <v>-649.5340021244156</v>
       </c>
       <c r="D65">
-        <v>298.2009631521438</v>
+        <v>294.2179978755846</v>
       </c>
       <c r="E65">
-        <v>189.359</v>
+        <v>204.652</v>
       </c>
       <c r="F65">
-        <v>963.4590000000002</v>
+        <v>978.7520000000002</v>
       </c>
       <c r="G65">
         <v>35</v>
@@ -6611,37 +6611,37 @@
         <v>66.5</v>
       </c>
       <c r="M65">
-        <v>227.1836322000001</v>
+        <v>230.7897216000001</v>
       </c>
       <c r="N65">
-        <v>-160.6836322000001</v>
+        <v>-164.2897216000001</v>
       </c>
       <c r="O65">
-        <v>-32.13672644000001</v>
+        <v>-32.85794432000002</v>
       </c>
       <c r="P65">
-        <v>-128.54690576</v>
+        <v>-131.4317772800001</v>
       </c>
       <c r="Q65">
-        <v>-83.74690576000005</v>
+        <v>-86.63177728000007</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1251190529655415</v>
+        <v>0.1273223599923621</v>
       </c>
       <c r="T65">
-        <v>1.504653124552917</v>
+        <v>1.546449044679387</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0585429499088711</v>
+        <v>0.05762821631654499</v>
       </c>
       <c r="W65">
-        <v>0.2219955724114882</v>
+        <v>0.2222112665925587</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2927147495443555</v>
+        <v>0.288141081582725</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1880512602164879</v>
+        <v>0.1899512602164879</v>
       </c>
       <c r="C66">
-        <v>-649.5340021244156</v>
+        <v>-668.7049716622753</v>
       </c>
       <c r="D66">
-        <v>294.2179978755846</v>
+        <v>290.3400283377249</v>
       </c>
       <c r="E66">
-        <v>204.652</v>
+        <v>219.9450000000001</v>
       </c>
       <c r="F66">
-        <v>978.7520000000002</v>
+        <v>994.0450000000002</v>
       </c>
       <c r="G66">
         <v>35</v>
@@ -6693,37 +6693,37 @@
         <v>66.5</v>
       </c>
       <c r="M66">
-        <v>230.7897216000001</v>
+        <v>234.3958110000001</v>
       </c>
       <c r="N66">
-        <v>-164.2897216000001</v>
+        <v>-167.8958110000001</v>
       </c>
       <c r="O66">
-        <v>-32.85794432000002</v>
+        <v>-33.57916220000001</v>
       </c>
       <c r="P66">
-        <v>-131.4317772800001</v>
+        <v>-134.3166488000001</v>
       </c>
       <c r="Q66">
-        <v>-86.63177728000007</v>
+        <v>-89.51664880000006</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1273223599923621</v>
+        <v>0.1296515702778582</v>
       </c>
       <c r="T66">
-        <v>1.546449044679387</v>
+        <v>1.590633303098798</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05762821631654499</v>
+        <v>0.05674162837321353</v>
       </c>
       <c r="W66">
-        <v>0.2222112665925587</v>
+        <v>0.2224203240295963</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.288141081582725</v>
+        <v>0.2837081418660676</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1899512602164879</v>
+        <v>0.1918512602164879</v>
       </c>
       <c r="C67">
-        <v>-668.7049716622753</v>
+        <v>-687.7750431714426</v>
       </c>
       <c r="D67">
-        <v>290.3400283377249</v>
+        <v>286.5629568285576</v>
       </c>
       <c r="E67">
-        <v>219.9450000000001</v>
+        <v>235.2380000000001</v>
       </c>
       <c r="F67">
-        <v>994.0450000000002</v>
+        <v>1009.338</v>
       </c>
       <c r="G67">
         <v>35</v>
@@ -6775,37 +6775,37 @@
         <v>66.5</v>
       </c>
       <c r="M67">
-        <v>234.3958110000001</v>
+        <v>238.0019004000001</v>
       </c>
       <c r="N67">
-        <v>-167.8958110000001</v>
+        <v>-171.5019004000001</v>
       </c>
       <c r="O67">
-        <v>-33.57916220000001</v>
+        <v>-34.30038008000002</v>
       </c>
       <c r="P67">
-        <v>-134.3166488000001</v>
+        <v>-137.20152032</v>
       </c>
       <c r="Q67">
-        <v>-89.51664880000006</v>
+        <v>-92.40152032000005</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1296515702778582</v>
+        <v>0.1321177929330893</v>
       </c>
       <c r="T67">
-        <v>1.590633303098798</v>
+        <v>1.63741663554288</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05674162837321353</v>
+        <v>0.05588190673119514</v>
       </c>
       <c r="W67">
-        <v>0.2224203240295963</v>
+        <v>0.2226230463927842</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2837081418660676</v>
+        <v>0.2794095336559758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1918512602164879</v>
+        <v>0.1937512602164879</v>
       </c>
       <c r="C68">
-        <v>-687.7750431714426</v>
+        <v>-706.7481038696587</v>
       </c>
       <c r="D68">
-        <v>286.5629568285576</v>
+        <v>282.8828961303413</v>
       </c>
       <c r="E68">
-        <v>235.2380000000001</v>
+        <v>250.5309999999999</v>
       </c>
       <c r="F68">
-        <v>1009.338</v>
+        <v>1024.631</v>
       </c>
       <c r="G68">
         <v>35</v>
@@ -6857,37 +6857,37 @@
         <v>66.5</v>
       </c>
       <c r="M68">
-        <v>238.0019004000001</v>
+        <v>241.6079898</v>
       </c>
       <c r="N68">
-        <v>-171.5019004000001</v>
+        <v>-175.1079898</v>
       </c>
       <c r="O68">
-        <v>-34.30038008000002</v>
+        <v>-35.02159796000001</v>
       </c>
       <c r="P68">
-        <v>-137.20152032</v>
+        <v>-140.08639184</v>
       </c>
       <c r="Q68">
-        <v>-92.40152032000005</v>
+        <v>-95.28639184000004</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1321177929330893</v>
+        <v>0.1347334836280314</v>
       </c>
       <c r="T68">
-        <v>1.63741663554288</v>
+        <v>1.687035321468422</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05588190673119514</v>
+        <v>0.05504784842177433</v>
       </c>
       <c r="W68">
-        <v>0.2226230463927842</v>
+        <v>0.2228197173421456</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2794095336559758</v>
+        <v>0.2752392421088716</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1937512602164879</v>
+        <v>0.1956512602164879</v>
       </c>
       <c r="C69">
-        <v>-706.7481038696587</v>
+        <v>-725.627843826808</v>
       </c>
       <c r="D69">
-        <v>282.8828961303413</v>
+        <v>279.2961561731922</v>
       </c>
       <c r="E69">
-        <v>250.5309999999999</v>
+        <v>265.8240000000001</v>
       </c>
       <c r="F69">
-        <v>1024.631</v>
+        <v>1039.924</v>
       </c>
       <c r="G69">
         <v>35</v>
@@ -6939,37 +6939,37 @@
         <v>66.5</v>
       </c>
       <c r="M69">
-        <v>241.6079898</v>
+        <v>245.2140792000001</v>
       </c>
       <c r="N69">
-        <v>-175.1079898</v>
+        <v>-178.7140792000001</v>
       </c>
       <c r="O69">
-        <v>-35.02159796000001</v>
+        <v>-35.74281584000001</v>
       </c>
       <c r="P69">
-        <v>-140.08639184</v>
+        <v>-142.9712633600001</v>
       </c>
       <c r="Q69">
-        <v>-95.28639184000004</v>
+        <v>-98.17126336000005</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1347334836280314</v>
+        <v>0.1375126549914074</v>
       </c>
       <c r="T69">
-        <v>1.687035321468422</v>
+        <v>1.73975517526431</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05504784842177433</v>
+        <v>0.05423832123910118</v>
       </c>
       <c r="W69">
-        <v>0.2228197173421456</v>
+        <v>0.2230106038518199</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2752392421088716</v>
+        <v>0.2711916061955059</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1956512602164879</v>
+        <v>0.1975512602164879</v>
       </c>
       <c r="C70">
-        <v>-725.627843826808</v>
+        <v>-744.4177683068556</v>
       </c>
       <c r="D70">
-        <v>279.2961561731922</v>
+        <v>275.7992316931447</v>
       </c>
       <c r="E70">
-        <v>265.8240000000001</v>
+        <v>281.1170000000002</v>
       </c>
       <c r="F70">
-        <v>1039.924</v>
+        <v>1055.217</v>
       </c>
       <c r="G70">
         <v>35</v>
@@ -7021,37 +7021,37 @@
         <v>66.5</v>
       </c>
       <c r="M70">
-        <v>245.2140792000001</v>
+        <v>248.8201686000001</v>
       </c>
       <c r="N70">
-        <v>-178.7140792000001</v>
+        <v>-182.3201686000001</v>
       </c>
       <c r="O70">
-        <v>-35.74281584000001</v>
+        <v>-36.46403372000002</v>
       </c>
       <c r="P70">
-        <v>-142.9712633600001</v>
+        <v>-145.8561348800001</v>
       </c>
       <c r="Q70">
-        <v>-98.17126336000005</v>
+        <v>-101.0561348800001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1375126549914074</v>
+        <v>0.1404711277330657</v>
       </c>
       <c r="T70">
-        <v>1.73975517526431</v>
+        <v>1.795876309950256</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05423832123910118</v>
+        <v>0.05345225861244753</v>
       </c>
       <c r="W70">
-        <v>0.2230106038518199</v>
+        <v>0.2231959574191849</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2711916061955059</v>
+        <v>0.2672612930622377</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1975512602164879</v>
+        <v>0.1994512602164879</v>
       </c>
       <c r="C71">
-        <v>-744.4177683068556</v>
+        <v>-763.1212091940869</v>
       </c>
       <c r="D71">
-        <v>275.7992316931447</v>
+        <v>272.3887908059133</v>
       </c>
       <c r="E71">
-        <v>281.1170000000002</v>
+        <v>296.4100000000001</v>
       </c>
       <c r="F71">
-        <v>1055.217</v>
+        <v>1070.51</v>
       </c>
       <c r="G71">
         <v>35</v>
@@ -7103,37 +7103,37 @@
         <v>66.5</v>
       </c>
       <c r="M71">
-        <v>248.8201686000001</v>
+        <v>252.4262580000001</v>
       </c>
       <c r="N71">
-        <v>-182.3201686000001</v>
+        <v>-185.9262580000001</v>
       </c>
       <c r="O71">
-        <v>-36.46403372000002</v>
+        <v>-37.18525160000002</v>
       </c>
       <c r="P71">
-        <v>-145.8561348800001</v>
+        <v>-148.7410064000001</v>
       </c>
       <c r="Q71">
-        <v>-101.0561348800001</v>
+        <v>-103.9410064000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1404711277330657</v>
+        <v>0.1436268319908345</v>
       </c>
       <c r="T71">
-        <v>1.795876309950256</v>
+        <v>1.855738853615265</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05345225861244753</v>
+        <v>0.052688654917984</v>
       </c>
       <c r="W71">
-        <v>0.2231959574191849</v>
+        <v>0.2233760151703394</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2672612930622377</v>
+        <v>0.26344327458992</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1994512602164879</v>
+        <v>0.2013512602164879</v>
       </c>
       <c r="C72">
-        <v>-763.1212091940869</v>
+        <v>-781.7413355819475</v>
       </c>
       <c r="D72">
-        <v>272.3887908059133</v>
+        <v>269.0616644180528</v>
       </c>
       <c r="E72">
-        <v>296.4100000000001</v>
+        <v>311.7030000000002</v>
       </c>
       <c r="F72">
-        <v>1070.51</v>
+        <v>1085.803</v>
       </c>
       <c r="G72">
         <v>35</v>
@@ -7185,37 +7185,37 @@
         <v>66.5</v>
       </c>
       <c r="M72">
-        <v>252.4262580000001</v>
+        <v>256.0323474000001</v>
       </c>
       <c r="N72">
-        <v>-185.9262580000001</v>
+        <v>-189.5323474000001</v>
       </c>
       <c r="O72">
-        <v>-37.18525160000002</v>
+        <v>-37.90646948000002</v>
       </c>
       <c r="P72">
-        <v>-148.7410064000001</v>
+        <v>-151.6258779200001</v>
       </c>
       <c r="Q72">
-        <v>-103.9410064000001</v>
+        <v>-106.8258779200001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1436268319908345</v>
+        <v>0.1470001710250013</v>
       </c>
       <c r="T72">
-        <v>1.855738853615265</v>
+        <v>1.919729848567515</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.052688654917984</v>
+        <v>0.05194656118674478</v>
       </c>
       <c r="W72">
-        <v>0.2233760151703394</v>
+        <v>0.2235510008721656</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.26344327458992</v>
+        <v>0.2597328059337238</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2013512602164879</v>
+        <v>0.2032512602164879</v>
       </c>
       <c r="C73">
-        <v>-781.7413355819474</v>
+        <v>-800.2811635952091</v>
       </c>
       <c r="D73">
-        <v>269.0616644180527</v>
+        <v>265.8148364047909</v>
       </c>
       <c r="E73">
-        <v>311.703</v>
+        <v>326.9959999999999</v>
       </c>
       <c r="F73">
-        <v>1085.803</v>
+        <v>1101.096</v>
       </c>
       <c r="G73">
         <v>35</v>
@@ -7267,37 +7267,37 @@
         <v>66.5</v>
       </c>
       <c r="M73">
-        <v>256.0323474</v>
+        <v>259.6384368</v>
       </c>
       <c r="N73">
-        <v>-189.5323474</v>
+        <v>-193.1384368</v>
       </c>
       <c r="O73">
-        <v>-37.90646948000001</v>
+        <v>-38.62768736000001</v>
       </c>
       <c r="P73">
-        <v>-151.6258779200001</v>
+        <v>-154.51074944</v>
       </c>
       <c r="Q73">
-        <v>-106.8258779200001</v>
+        <v>-109.71074944</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1470001710250012</v>
+        <v>0.1506144628473227</v>
       </c>
       <c r="T73">
-        <v>1.919729848567515</v>
+        <v>1.988291628873497</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05194656118674479</v>
+        <v>0.05122508117026223</v>
       </c>
       <c r="W73">
-        <v>0.2235510008721656</v>
+        <v>0.2237211258600522</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2597328059337239</v>
+        <v>0.2561254058513112</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2032512602164879</v>
+        <v>0.2051512602164879</v>
       </c>
       <c r="C74">
-        <v>-800.2811635952091</v>
+        <v>-818.7435655094648</v>
       </c>
       <c r="D74">
-        <v>265.8148364047909</v>
+        <v>262.6454344905354</v>
       </c>
       <c r="E74">
-        <v>326.9959999999999</v>
+        <v>342.289</v>
       </c>
       <c r="F74">
-        <v>1101.096</v>
+        <v>1116.389</v>
       </c>
       <c r="G74">
         <v>35</v>
@@ -7349,37 +7349,37 @@
         <v>66.5</v>
       </c>
       <c r="M74">
-        <v>259.6384368</v>
+        <v>263.2445262000001</v>
       </c>
       <c r="N74">
-        <v>-193.1384368</v>
+        <v>-196.7445262000001</v>
       </c>
       <c r="O74">
-        <v>-38.62768736000001</v>
+        <v>-39.34890524000001</v>
       </c>
       <c r="P74">
-        <v>-154.51074944</v>
+        <v>-157.39562096</v>
       </c>
       <c r="Q74">
-        <v>-109.71074944</v>
+        <v>-112.59562096</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1506144628473227</v>
+        <v>0.1544964799898161</v>
       </c>
       <c r="T74">
-        <v>1.988291628873497</v>
+        <v>2.061932059572515</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05122508117026223</v>
+        <v>0.0505233677295737</v>
       </c>
       <c r="W74">
-        <v>0.2237211258600522</v>
+        <v>0.2238865898893665</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2561254058513112</v>
+        <v>0.2526168386478684</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2051512602164879</v>
+        <v>0.2070512602164879</v>
       </c>
       <c r="C75">
-        <v>-818.7435655094648</v>
+        <v>-837.1312782258925</v>
       </c>
       <c r="D75">
-        <v>262.6454344905354</v>
+        <v>259.5507217741075</v>
       </c>
       <c r="E75">
-        <v>342.289</v>
+        <v>357.5819999999999</v>
       </c>
       <c r="F75">
-        <v>1116.389</v>
+        <v>1131.682</v>
       </c>
       <c r="G75">
         <v>35</v>
@@ -7431,37 +7431,37 @@
         <v>66.5</v>
       </c>
       <c r="M75">
-        <v>263.2445262000001</v>
+        <v>266.8506156</v>
       </c>
       <c r="N75">
-        <v>-196.7445262000001</v>
+        <v>-200.3506156</v>
       </c>
       <c r="O75">
-        <v>-39.34890524000001</v>
+        <v>-40.07012312000001</v>
       </c>
       <c r="P75">
-        <v>-157.39562096</v>
+        <v>-160.28049248</v>
       </c>
       <c r="Q75">
-        <v>-112.59562096</v>
+        <v>-115.48049248</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1544964799898161</v>
+        <v>0.1586771138355783</v>
       </c>
       <c r="T75">
-        <v>2.061932059572515</v>
+        <v>2.141237138786843</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0505233677295737</v>
+        <v>0.0498406195170119</v>
       </c>
       <c r="W75">
-        <v>0.2238865898893665</v>
+        <v>0.2240475819178886</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2526168386478684</v>
+        <v>0.2492030975850594</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2070512602164879</v>
+        <v>0.2089512602164879</v>
       </c>
       <c r="C76">
-        <v>-837.1312782258925</v>
+        <v>-855.4469111538665</v>
       </c>
       <c r="D76">
-        <v>259.5507217741075</v>
+        <v>256.5280888461336</v>
       </c>
       <c r="E76">
-        <v>357.5819999999999</v>
+        <v>372.875</v>
       </c>
       <c r="F76">
-        <v>1131.682</v>
+        <v>1146.975</v>
       </c>
       <c r="G76">
         <v>35</v>
@@ -7513,37 +7513,37 @@
         <v>66.5</v>
       </c>
       <c r="M76">
-        <v>266.8506156</v>
+        <v>270.4567050000001</v>
       </c>
       <c r="N76">
-        <v>-200.3506156</v>
+        <v>-203.9567050000001</v>
       </c>
       <c r="O76">
-        <v>-40.07012312000001</v>
+        <v>-40.79134100000002</v>
       </c>
       <c r="P76">
-        <v>-160.28049248</v>
+        <v>-163.165364</v>
       </c>
       <c r="Q76">
-        <v>-115.48049248</v>
+        <v>-118.365364</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1586771138355783</v>
+        <v>0.1631921983890015</v>
       </c>
       <c r="T76">
-        <v>2.141237138786843</v>
+        <v>2.226886624338317</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0498406195170119</v>
+        <v>0.04917607792345174</v>
       </c>
       <c r="W76">
-        <v>0.2240475819178886</v>
+        <v>0.2242042808256501</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2492030975850594</v>
+        <v>0.2458803896172587</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2089512602164879</v>
+        <v>0.2108512602164879</v>
       </c>
       <c r="C77">
-        <v>-855.4469111538665</v>
+        <v>-873.6929535491104</v>
       </c>
       <c r="D77">
-        <v>256.5280888461336</v>
+        <v>253.5750464508899</v>
       </c>
       <c r="E77">
-        <v>372.875</v>
+        <v>388.1680000000001</v>
       </c>
       <c r="F77">
-        <v>1146.975</v>
+        <v>1162.268</v>
       </c>
       <c r="G77">
         <v>35</v>
@@ -7595,37 +7595,37 @@
         <v>66.5</v>
       </c>
       <c r="M77">
-        <v>270.4567050000001</v>
+        <v>274.0627944000001</v>
       </c>
       <c r="N77">
-        <v>-203.9567050000001</v>
+        <v>-207.5627944000001</v>
       </c>
       <c r="O77">
-        <v>-40.79134100000002</v>
+        <v>-41.51255888000002</v>
       </c>
       <c r="P77">
-        <v>-163.165364</v>
+        <v>-166.0502355200001</v>
       </c>
       <c r="Q77">
-        <v>-118.365364</v>
+        <v>-121.2502355200001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1631921983890015</v>
+        <v>0.1680835399885431</v>
       </c>
       <c r="T77">
-        <v>2.226886624338317</v>
+        <v>2.31967356701908</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04917607792345174</v>
+        <v>0.04852902426656421</v>
       </c>
       <c r="W77">
-        <v>0.2242042808256501</v>
+        <v>0.2243568560779442</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2458803896172587</v>
+        <v>0.242645121332821</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2108512602164879</v>
+        <v>0.2127512602164879</v>
       </c>
       <c r="C78">
-        <v>-873.6929535491104</v>
+        <v>-891.8717813507809</v>
       </c>
       <c r="D78">
-        <v>253.5750464508899</v>
+        <v>250.6892186492193</v>
       </c>
       <c r="E78">
-        <v>388.1680000000001</v>
+        <v>403.461</v>
       </c>
       <c r="F78">
-        <v>1162.268</v>
+        <v>1177.561</v>
       </c>
       <c r="G78">
         <v>35</v>
@@ -7677,37 +7677,37 @@
         <v>66.5</v>
       </c>
       <c r="M78">
-        <v>274.0627944000001</v>
+        <v>277.6688838000001</v>
       </c>
       <c r="N78">
-        <v>-207.5627944000001</v>
+        <v>-211.1688838000001</v>
       </c>
       <c r="O78">
-        <v>-41.51255888000002</v>
+        <v>-42.23377676000001</v>
       </c>
       <c r="P78">
-        <v>-166.0502355200001</v>
+        <v>-168.93510704</v>
       </c>
       <c r="Q78">
-        <v>-121.2502355200001</v>
+        <v>-124.1351070400001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1680835399885431</v>
+        <v>0.173400215640219</v>
       </c>
       <c r="T78">
-        <v>2.31967356701908</v>
+        <v>2.420528939498171</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04852902426656421</v>
+        <v>0.04789877719816727</v>
       </c>
       <c r="W78">
-        <v>0.2243568560779442</v>
+        <v>0.2245054683366722</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.242645121332821</v>
+        <v>0.2394938859908363</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2127512602164879</v>
+        <v>0.2146512602164879</v>
       </c>
       <c r="C79">
-        <v>-891.8717813507809</v>
+        <v>-909.9856635569474</v>
       </c>
       <c r="D79">
-        <v>250.6892186492193</v>
+        <v>247.8683364430529</v>
       </c>
       <c r="E79">
-        <v>403.461</v>
+        <v>418.7540000000001</v>
       </c>
       <c r="F79">
-        <v>1177.561</v>
+        <v>1192.854</v>
       </c>
       <c r="G79">
         <v>35</v>
@@ -7759,37 +7759,37 @@
         <v>66.5</v>
       </c>
       <c r="M79">
-        <v>277.6688838000001</v>
+        <v>281.2749732000001</v>
       </c>
       <c r="N79">
-        <v>-211.1688838000001</v>
+        <v>-214.7749732000001</v>
       </c>
       <c r="O79">
-        <v>-42.23377676000001</v>
+        <v>-42.95499464000002</v>
       </c>
       <c r="P79">
-        <v>-168.93510704</v>
+        <v>-171.8199785600001</v>
       </c>
       <c r="Q79">
-        <v>-124.1351070400001</v>
+        <v>-127.0199785600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.173400215640219</v>
+        <v>0.1792002254420471</v>
       </c>
       <c r="T79">
-        <v>2.420528939498171</v>
+        <v>2.530552982202633</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04789877719816727</v>
+        <v>0.04728469031101128</v>
       </c>
       <c r="W79">
-        <v>0.2245054683366722</v>
+        <v>0.2246502700246636</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2394938859908363</v>
+        <v>0.2364234515550564</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2146512602164879</v>
+        <v>0.2165512602164879</v>
       </c>
       <c r="C80">
-        <v>-909.9856635569474</v>
+        <v>-928.0367681744167</v>
       </c>
       <c r="D80">
-        <v>247.8683364430529</v>
+        <v>245.1102318255835</v>
       </c>
       <c r="E80">
-        <v>418.7540000000001</v>
+        <v>434.047</v>
       </c>
       <c r="F80">
-        <v>1192.854</v>
+        <v>1208.147</v>
       </c>
       <c r="G80">
         <v>35</v>
@@ -7841,37 +7841,37 @@
         <v>66.5</v>
       </c>
       <c r="M80">
-        <v>281.2749732000001</v>
+        <v>284.8810626000001</v>
       </c>
       <c r="N80">
-        <v>-214.7749732000001</v>
+        <v>-218.3810626000001</v>
       </c>
       <c r="O80">
-        <v>-42.95499464000002</v>
+        <v>-43.67621252000001</v>
       </c>
       <c r="P80">
-        <v>-171.8199785600001</v>
+        <v>-174.7048500800001</v>
       </c>
       <c r="Q80">
-        <v>-127.0199785600001</v>
+        <v>-129.9048500800001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1792002254420471</v>
+        <v>0.1855526171297636</v>
       </c>
       <c r="T80">
-        <v>2.530552982202633</v>
+        <v>2.651055505164664</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04728469031101128</v>
+        <v>0.04668614992732759</v>
       </c>
       <c r="W80">
-        <v>0.2246502700246636</v>
+        <v>0.2247914058471362</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2364234515550564</v>
+        <v>0.2334307496366379</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2165512602164879</v>
+        <v>0.2184512602164879</v>
       </c>
       <c r="C81">
-        <v>-928.0367681744167</v>
+        <v>-946.027167775698</v>
       </c>
       <c r="D81">
-        <v>245.1102318255835</v>
+        <v>242.4128322243023</v>
       </c>
       <c r="E81">
-        <v>434.047</v>
+        <v>449.3400000000001</v>
       </c>
       <c r="F81">
-        <v>1208.147</v>
+        <v>1223.44</v>
       </c>
       <c r="G81">
         <v>35</v>
@@ -7923,37 +7923,37 @@
         <v>66.5</v>
       </c>
       <c r="M81">
-        <v>284.8810626000001</v>
+        <v>288.4871520000001</v>
       </c>
       <c r="N81">
-        <v>-218.3810626000001</v>
+        <v>-221.9871520000001</v>
       </c>
       <c r="O81">
-        <v>-43.67621252000001</v>
+        <v>-44.39743040000002</v>
       </c>
       <c r="P81">
-        <v>-174.7048500800001</v>
+        <v>-177.5897216000001</v>
       </c>
       <c r="Q81">
-        <v>-129.9048500800001</v>
+        <v>-132.7897216000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1855526171297636</v>
+        <v>0.1925402479862518</v>
       </c>
       <c r="T81">
-        <v>2.651055505164664</v>
+        <v>2.783608280422897</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04668614992732759</v>
+        <v>0.04610257305323599</v>
       </c>
       <c r="W81">
-        <v>0.2247914058471362</v>
+        <v>0.224929013274047</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2334307496366379</v>
+        <v>0.23051286526618</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2184512602164879</v>
+        <v>0.220351260216488</v>
       </c>
       <c r="C82">
-        <v>-946.027167775698</v>
+        <v>-963.9588446930395</v>
       </c>
       <c r="D82">
-        <v>242.4128322243023</v>
+        <v>239.7741553069606</v>
       </c>
       <c r="E82">
-        <v>449.3400000000001</v>
+        <v>464.633</v>
       </c>
       <c r="F82">
-        <v>1223.44</v>
+        <v>1238.733</v>
       </c>
       <c r="G82">
         <v>35</v>
@@ -8005,37 +8005,37 @@
         <v>66.5</v>
       </c>
       <c r="M82">
-        <v>288.4871520000001</v>
+        <v>292.0932414000001</v>
       </c>
       <c r="N82">
-        <v>-221.9871520000001</v>
+        <v>-225.5932414000001</v>
       </c>
       <c r="O82">
-        <v>-44.39743040000002</v>
+        <v>-45.11864828000002</v>
       </c>
       <c r="P82">
-        <v>-177.5897216000001</v>
+        <v>-180.4745931200001</v>
       </c>
       <c r="Q82">
-        <v>-132.7897216000001</v>
+        <v>-135.6745931200001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1925402479862518</v>
+        <v>0.2002634189328967</v>
       </c>
       <c r="T82">
-        <v>2.783608280422897</v>
+        <v>2.930113979392523</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04610257305323599</v>
+        <v>0.04553340548467753</v>
       </c>
       <c r="W82">
-        <v>0.224929013274047</v>
+        <v>0.2250632229867131</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.23051286526618</v>
+        <v>0.2276670274233876</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.220351260216488</v>
+        <v>0.2222512602164879</v>
       </c>
       <c r="C83">
-        <v>-963.9588446930395</v>
+        <v>-981.8336958768979</v>
       </c>
       <c r="D83">
-        <v>239.7741553069606</v>
+        <v>237.1923041231024</v>
       </c>
       <c r="E83">
-        <v>464.633</v>
+        <v>479.9260000000002</v>
       </c>
       <c r="F83">
-        <v>1238.733</v>
+        <v>1254.026</v>
       </c>
       <c r="G83">
         <v>35</v>
@@ -8087,37 +8087,37 @@
         <v>66.5</v>
       </c>
       <c r="M83">
-        <v>292.0932414000001</v>
+        <v>295.6993308000001</v>
       </c>
       <c r="N83">
-        <v>-225.5932414000001</v>
+        <v>-229.1993308000001</v>
       </c>
       <c r="O83">
-        <v>-45.11864828000002</v>
+        <v>-45.83986616000002</v>
       </c>
       <c r="P83">
-        <v>-180.4745931200001</v>
+        <v>-183.3594646400001</v>
       </c>
       <c r="Q83">
-        <v>-135.6745931200001</v>
+        <v>-138.5594646400001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2002634189328967</v>
+        <v>0.2088447199847243</v>
       </c>
       <c r="T83">
-        <v>2.930113979392523</v>
+        <v>3.092898089358775</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04553340548467753</v>
+        <v>0.04497812005193755</v>
       </c>
       <c r="W83">
-        <v>0.2250632229867131</v>
+        <v>0.2251941592917531</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2276670274233876</v>
+        <v>0.2248906002596878</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2222512602164879</v>
+        <v>0.224151260216488</v>
       </c>
       <c r="C84">
-        <v>-981.8336958768979</v>
+        <v>-999.6535374438533</v>
       </c>
       <c r="D84">
-        <v>237.1923041231024</v>
+        <v>234.6654625561468</v>
       </c>
       <c r="E84">
-        <v>479.9260000000002</v>
+        <v>495.2190000000001</v>
       </c>
       <c r="F84">
-        <v>1254.026</v>
+        <v>1269.319</v>
       </c>
       <c r="G84">
         <v>35</v>
@@ -8169,37 +8169,37 @@
         <v>66.5</v>
       </c>
       <c r="M84">
-        <v>295.6993308000001</v>
+        <v>299.3054202000001</v>
       </c>
       <c r="N84">
-        <v>-229.1993308000001</v>
+        <v>-232.8054202000001</v>
       </c>
       <c r="O84">
-        <v>-45.83986616000002</v>
+        <v>-46.56108404000002</v>
       </c>
       <c r="P84">
-        <v>-183.3594646400001</v>
+        <v>-186.24433616</v>
       </c>
       <c r="Q84">
-        <v>-138.5594646400001</v>
+        <v>-141.44433616</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2088447199847243</v>
+        <v>0.2184355858661786</v>
       </c>
       <c r="T84">
-        <v>3.092898089358775</v>
+        <v>3.274833271085761</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04497812005193755</v>
+        <v>0.04443621499107084</v>
       </c>
       <c r="W84">
-        <v>0.2251941592917531</v>
+        <v>0.2253219405051055</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2248906002596878</v>
+        <v>0.2221810749553542</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.224151260216488</v>
+        <v>0.226051260216488</v>
       </c>
       <c r="C85">
-        <v>-999.6535374438533</v>
+        <v>-1017.420108936897</v>
       </c>
       <c r="D85">
-        <v>234.6654625561468</v>
+        <v>232.1918910631032</v>
       </c>
       <c r="E85">
-        <v>495.2190000000001</v>
+        <v>510.5120000000002</v>
       </c>
       <c r="F85">
-        <v>1269.319</v>
+        <v>1284.612</v>
       </c>
       <c r="G85">
         <v>35</v>
@@ -8251,37 +8251,37 @@
         <v>66.5</v>
       </c>
       <c r="M85">
-        <v>299.3054202000001</v>
+        <v>302.9115096000001</v>
       </c>
       <c r="N85">
-        <v>-232.8054202000001</v>
+        <v>-236.4115096000001</v>
       </c>
       <c r="O85">
-        <v>-46.56108404000002</v>
+        <v>-47.28230192000002</v>
       </c>
       <c r="P85">
-        <v>-186.24433616</v>
+        <v>-189.1292076800001</v>
       </c>
       <c r="Q85">
-        <v>-141.44433616</v>
+        <v>-144.3292076800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2184355858661786</v>
+        <v>0.2292253099828149</v>
       </c>
       <c r="T85">
-        <v>3.274833271085761</v>
+        <v>3.479510350528623</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04443621499107084</v>
+        <v>0.04390721243165333</v>
       </c>
       <c r="W85">
-        <v>0.2253219405051055</v>
+        <v>0.2254466793086162</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2221810749553542</v>
+        <v>0.2195360621582666</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2260512602164879</v>
+        <v>0.2279512602164879</v>
       </c>
       <c r="C86">
-        <v>-1017.420108936897</v>
+        <v>-1035.135077319084</v>
       </c>
       <c r="D86">
-        <v>232.1918910631034</v>
+        <v>229.769922680916</v>
       </c>
       <c r="E86">
-        <v>510.5119999999999</v>
+        <v>525.8050000000001</v>
       </c>
       <c r="F86">
-        <v>1284.612</v>
+        <v>1299.905</v>
       </c>
       <c r="G86">
         <v>35</v>
@@ -8333,37 +8333,37 @@
         <v>66.5</v>
       </c>
       <c r="M86">
-        <v>302.9115096</v>
+        <v>306.5175990000001</v>
       </c>
       <c r="N86">
-        <v>-236.4115096</v>
+        <v>-240.0175990000001</v>
       </c>
       <c r="O86">
-        <v>-47.28230192000001</v>
+        <v>-48.00351980000002</v>
       </c>
       <c r="P86">
-        <v>-189.12920768</v>
+        <v>-192.0140792000001</v>
       </c>
       <c r="Q86">
-        <v>-144.32920768</v>
+        <v>-147.2140792000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2292253099828147</v>
+        <v>0.241453663981669</v>
       </c>
       <c r="T86">
-        <v>3.47951035052862</v>
+        <v>3.711477707230528</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04390721243165333</v>
+        <v>0.04339065699128094</v>
       </c>
       <c r="W86">
-        <v>0.2254466793086162</v>
+        <v>0.225568483081456</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2195360621582667</v>
+        <v>0.2169532849564046</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2279512602164879</v>
+        <v>0.2298512602164879</v>
       </c>
       <c r="C87">
-        <v>-1035.135077319084</v>
+        <v>-1052.800040719825</v>
       </c>
       <c r="D87">
-        <v>229.769922680916</v>
+        <v>227.3979592801754</v>
       </c>
       <c r="E87">
-        <v>525.8050000000001</v>
+        <v>541.098</v>
       </c>
       <c r="F87">
-        <v>1299.905</v>
+        <v>1315.198</v>
       </c>
       <c r="G87">
         <v>35</v>
@@ -8415,37 +8415,37 @@
         <v>66.5</v>
       </c>
       <c r="M87">
-        <v>306.5175990000001</v>
+        <v>310.1236884</v>
       </c>
       <c r="N87">
-        <v>-240.0175990000001</v>
+        <v>-243.6236884</v>
       </c>
       <c r="O87">
-        <v>-48.00351980000002</v>
+        <v>-48.72473768000001</v>
       </c>
       <c r="P87">
-        <v>-192.0140792000001</v>
+        <v>-194.89895072</v>
       </c>
       <c r="Q87">
-        <v>-147.2140792000001</v>
+        <v>-150.0989507200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.241453663981669</v>
+        <v>0.2554289256946454</v>
       </c>
       <c r="T87">
-        <v>3.711477707230528</v>
+        <v>3.976583257746994</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04339065699128094</v>
+        <v>0.04288611446812651</v>
       </c>
       <c r="W87">
-        <v>0.225568483081456</v>
+        <v>0.2256874542084158</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2169532849564046</v>
+        <v>0.2144305723406326</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2298512602164879</v>
+        <v>0.2317512602164879</v>
       </c>
       <c r="C88">
-        <v>-1052.800040719825</v>
+        <v>-1070.416531951502</v>
       </c>
       <c r="D88">
-        <v>227.3979592801754</v>
+        <v>225.0744680484983</v>
       </c>
       <c r="E88">
-        <v>541.098</v>
+        <v>556.3910000000001</v>
       </c>
       <c r="F88">
-        <v>1315.198</v>
+        <v>1330.491</v>
       </c>
       <c r="G88">
         <v>35</v>
@@ -8497,37 +8497,37 @@
         <v>66.5</v>
       </c>
       <c r="M88">
-        <v>310.1236884</v>
+        <v>313.7297778000001</v>
       </c>
       <c r="N88">
-        <v>-243.6236884</v>
+        <v>-247.2297778000001</v>
       </c>
       <c r="O88">
-        <v>-48.72473768000001</v>
+        <v>-49.44595556000002</v>
       </c>
       <c r="P88">
-        <v>-194.89895072</v>
+        <v>-197.7838222400001</v>
       </c>
       <c r="Q88">
-        <v>-150.0989507200001</v>
+        <v>-152.9838222400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2554289256946454</v>
+        <v>0.2715542276711566</v>
       </c>
       <c r="T88">
-        <v>3.976583257746994</v>
+        <v>4.282474277573686</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04288611446812651</v>
+        <v>0.04239317062366529</v>
       </c>
       <c r="W88">
-        <v>0.2256874542084158</v>
+        <v>0.2258036903669397</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2144305723406326</v>
+        <v>0.2119658531183264</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2317512602164879</v>
+        <v>0.2336512602164879</v>
       </c>
       <c r="C89">
-        <v>-1070.416531951502</v>
+        <v>-1087.986021812679</v>
       </c>
       <c r="D89">
-        <v>225.0744680484983</v>
+        <v>222.797978187321</v>
       </c>
       <c r="E89">
-        <v>556.3910000000001</v>
+        <v>571.684</v>
       </c>
       <c r="F89">
-        <v>1330.491</v>
+        <v>1345.784</v>
       </c>
       <c r="G89">
         <v>35</v>
@@ -8579,37 +8579,37 @@
         <v>66.5</v>
       </c>
       <c r="M89">
-        <v>313.7297778000001</v>
+        <v>317.3358672000001</v>
       </c>
       <c r="N89">
-        <v>-247.2297778000001</v>
+        <v>-250.8358672000001</v>
       </c>
       <c r="O89">
-        <v>-49.44595556000002</v>
+        <v>-50.16717344000001</v>
       </c>
       <c r="P89">
-        <v>-197.7838222400001</v>
+        <v>-200.6686937600001</v>
       </c>
       <c r="Q89">
-        <v>-152.9838222400001</v>
+        <v>-155.86869376</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2715542276711566</v>
+        <v>0.2903670799770863</v>
       </c>
       <c r="T89">
-        <v>4.282474277573686</v>
+        <v>4.63934713403816</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04239317062366529</v>
+        <v>0.04191143004839637</v>
       </c>
       <c r="W89">
-        <v>0.2258036903669397</v>
+        <v>0.2259172847945881</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2119658531183264</v>
+        <v>0.2095571502419818</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2336512602164879</v>
+        <v>0.235551260216488</v>
       </c>
       <c r="C90">
-        <v>-1087.986021812679</v>
+        <v>-1105.509922192855</v>
       </c>
       <c r="D90">
-        <v>222.797978187321</v>
+        <v>220.5670778071449</v>
       </c>
       <c r="E90">
-        <v>571.684</v>
+        <v>586.9770000000001</v>
       </c>
       <c r="F90">
-        <v>1345.784</v>
+        <v>1361.077</v>
       </c>
       <c r="G90">
         <v>35</v>
@@ -8661,37 +8661,37 @@
         <v>66.5</v>
       </c>
       <c r="M90">
-        <v>317.3358672000001</v>
+        <v>320.9419566000001</v>
       </c>
       <c r="N90">
-        <v>-250.8358672000001</v>
+        <v>-254.4419566000001</v>
       </c>
       <c r="O90">
-        <v>-50.16717344000001</v>
+        <v>-50.88839132000002</v>
       </c>
       <c r="P90">
-        <v>-200.6686937600001</v>
+        <v>-203.5535652800001</v>
       </c>
       <c r="Q90">
-        <v>-155.86869376</v>
+        <v>-158.7535652800001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2903670799770863</v>
+        <v>0.3126004508840942</v>
       </c>
       <c r="T90">
-        <v>4.63934713403816</v>
+        <v>5.061105964405266</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04191143004839637</v>
+        <v>0.04144051510403236</v>
       </c>
       <c r="W90">
-        <v>0.2259172847945881</v>
+        <v>0.2260283265384692</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2095571502419818</v>
+        <v>0.2072025755201617</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.235551260216488</v>
+        <v>0.2374512602164879</v>
       </c>
       <c r="C91">
-        <v>-1105.509922192855</v>
+        <v>-1122.989588992542</v>
       </c>
       <c r="D91">
-        <v>220.5670778071449</v>
+        <v>218.3804110074579</v>
       </c>
       <c r="E91">
-        <v>586.9770000000001</v>
+        <v>602.27</v>
       </c>
       <c r="F91">
-        <v>1361.077</v>
+        <v>1376.37</v>
       </c>
       <c r="G91">
         <v>35</v>
@@ -8743,37 +8743,37 @@
         <v>66.5</v>
       </c>
       <c r="M91">
-        <v>320.9419566000001</v>
+        <v>324.5480460000001</v>
       </c>
       <c r="N91">
-        <v>-254.4419566000001</v>
+        <v>-258.0480460000001</v>
       </c>
       <c r="O91">
-        <v>-50.88839132000002</v>
+        <v>-51.60960920000002</v>
       </c>
       <c r="P91">
-        <v>-203.5535652800001</v>
+        <v>-206.4384368</v>
       </c>
       <c r="Q91">
-        <v>-158.7535652800001</v>
+        <v>-161.6384368</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3126004508840942</v>
+        <v>0.3392804959725036</v>
       </c>
       <c r="T91">
-        <v>5.061105964405266</v>
+        <v>5.567216560845793</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04144051510403236</v>
+        <v>0.04098006493620978</v>
       </c>
       <c r="W91">
-        <v>0.2260283265384692</v>
+        <v>0.2261369006880417</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2072025755201617</v>
+        <v>0.2049003246810489</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2374512602164879</v>
+        <v>0.2393512602164879</v>
       </c>
       <c r="C92">
-        <v>-1122.989588992542</v>
+        <v>-1140.426324871348</v>
       </c>
       <c r="D92">
-        <v>218.3804110074579</v>
+        <v>216.2366751286521</v>
       </c>
       <c r="E92">
-        <v>602.27</v>
+        <v>617.5630000000001</v>
       </c>
       <c r="F92">
-        <v>1376.37</v>
+        <v>1391.663</v>
       </c>
       <c r="G92">
         <v>35</v>
@@ -8825,37 +8825,37 @@
         <v>66.5</v>
       </c>
       <c r="M92">
-        <v>324.5480460000001</v>
+        <v>328.1541354000001</v>
       </c>
       <c r="N92">
-        <v>-258.0480460000001</v>
+        <v>-261.6541354000001</v>
       </c>
       <c r="O92">
-        <v>-51.60960920000002</v>
+        <v>-52.33082708000002</v>
       </c>
       <c r="P92">
-        <v>-206.4384368</v>
+        <v>-209.3233083200001</v>
       </c>
       <c r="Q92">
-        <v>-161.6384368</v>
+        <v>-164.5233083200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3392804959725036</v>
+        <v>0.3718894399694486</v>
       </c>
       <c r="T92">
-        <v>5.567216560845793</v>
+        <v>6.18579617871755</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04098006493620978</v>
+        <v>0.04052973455229539</v>
       </c>
       <c r="W92">
-        <v>0.2261369006880417</v>
+        <v>0.2262430885925688</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2049003246810489</v>
+        <v>0.2026486727614769</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2393512602164879</v>
+        <v>0.241251260216488</v>
       </c>
       <c r="C93">
-        <v>-1140.426324871348</v>
+        <v>-1157.821381835777</v>
       </c>
       <c r="D93">
-        <v>216.2366751286521</v>
+        <v>214.1346181642231</v>
       </c>
       <c r="E93">
-        <v>617.5630000000001</v>
+        <v>632.856</v>
       </c>
       <c r="F93">
-        <v>1391.663</v>
+        <v>1406.956</v>
       </c>
       <c r="G93">
         <v>35</v>
@@ -8907,37 +8907,37 @@
         <v>66.5</v>
       </c>
       <c r="M93">
-        <v>328.1541354000001</v>
+        <v>331.7602248000001</v>
       </c>
       <c r="N93">
-        <v>-261.6541354000001</v>
+        <v>-265.2602248000001</v>
       </c>
       <c r="O93">
-        <v>-52.33082708000002</v>
+        <v>-53.05204496000002</v>
       </c>
       <c r="P93">
-        <v>-209.3233083200001</v>
+        <v>-212.20817984</v>
       </c>
       <c r="Q93">
-        <v>-164.5233083200001</v>
+        <v>-167.4081798400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3718894399694486</v>
+        <v>0.4126506199656297</v>
       </c>
       <c r="T93">
-        <v>6.18579617871755</v>
+        <v>6.959020701057246</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04052973455229539</v>
+        <v>0.04008919395933565</v>
       </c>
       <c r="W93">
-        <v>0.2262430885925688</v>
+        <v>0.2263469680643887</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2026486727614769</v>
+        <v>0.2004459697966783</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.241251260216488</v>
+        <v>0.2431512602164879</v>
       </c>
       <c r="C94">
-        <v>-1157.821381835777</v>
+        <v>-1175.175963677544</v>
       </c>
       <c r="D94">
-        <v>214.1346181642231</v>
+        <v>212.0730363224567</v>
       </c>
       <c r="E94">
-        <v>632.856</v>
+        <v>648.1490000000001</v>
       </c>
       <c r="F94">
-        <v>1406.956</v>
+        <v>1422.249</v>
       </c>
       <c r="G94">
         <v>35</v>
@@ -8989,37 +8989,37 @@
         <v>66.5</v>
       </c>
       <c r="M94">
-        <v>331.7602248000001</v>
+        <v>335.3663142000001</v>
       </c>
       <c r="N94">
-        <v>-265.2602248000001</v>
+        <v>-268.8663142000001</v>
       </c>
       <c r="O94">
-        <v>-53.05204496000002</v>
+        <v>-53.77326284000002</v>
       </c>
       <c r="P94">
-        <v>-212.20817984</v>
+        <v>-215.0930513600001</v>
       </c>
       <c r="Q94">
-        <v>-167.4081798400001</v>
+        <v>-170.29305136</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4126506199656297</v>
+        <v>0.4650578513892911</v>
       </c>
       <c r="T94">
-        <v>6.959020701057246</v>
+        <v>7.953166515493995</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04008919395933565</v>
+        <v>0.03965812735762236</v>
       </c>
       <c r="W94">
-        <v>0.2263469680643887</v>
+        <v>0.2264486135690726</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2004459697966783</v>
+        <v>0.1982906367881118</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2431512602164879</v>
+        <v>0.2450512602164879</v>
       </c>
       <c r="C95">
-        <v>-1175.175963677544</v>
+        <v>-1192.491228272382</v>
       </c>
       <c r="D95">
-        <v>212.0730363224567</v>
+        <v>210.0507717276186</v>
       </c>
       <c r="E95">
-        <v>648.1490000000001</v>
+        <v>663.4420000000002</v>
       </c>
       <c r="F95">
-        <v>1422.249</v>
+        <v>1437.542</v>
       </c>
       <c r="G95">
         <v>35</v>
@@ -9071,37 +9071,37 @@
         <v>66.5</v>
       </c>
       <c r="M95">
-        <v>335.3663142000001</v>
+        <v>338.9724036000001</v>
       </c>
       <c r="N95">
-        <v>-268.8663142000001</v>
+        <v>-272.4724036000001</v>
       </c>
       <c r="O95">
-        <v>-53.77326284000002</v>
+        <v>-54.49448072000003</v>
       </c>
       <c r="P95">
-        <v>-215.0930513600001</v>
+        <v>-217.9779228800001</v>
       </c>
       <c r="Q95">
-        <v>-170.29305136</v>
+        <v>-173.1779228800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4650578513892911</v>
+        <v>0.5349341599541731</v>
       </c>
       <c r="T95">
-        <v>7.953166515493995</v>
+        <v>9.278694268076331</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03965812735762236</v>
+        <v>0.03923623238573276</v>
       </c>
       <c r="W95">
-        <v>0.2264486135690726</v>
+        <v>0.2265480964034442</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1982906367881118</v>
+        <v>0.1961811619286637</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2450512602164879</v>
+        <v>0.2469512602164879</v>
       </c>
       <c r="C96">
-        <v>-1192.491228272382</v>
+        <v>-1209.768289748571</v>
       </c>
       <c r="D96">
-        <v>210.0507717276186</v>
+        <v>208.0667102514292</v>
       </c>
       <c r="E96">
-        <v>663.4420000000002</v>
+        <v>678.7350000000001</v>
       </c>
       <c r="F96">
-        <v>1437.542</v>
+        <v>1452.835</v>
       </c>
       <c r="G96">
         <v>35</v>
@@ -9153,37 +9153,37 @@
         <v>66.5</v>
       </c>
       <c r="M96">
-        <v>338.9724036000001</v>
+        <v>342.5784930000001</v>
       </c>
       <c r="N96">
-        <v>-272.4724036000001</v>
+        <v>-276.0784930000001</v>
       </c>
       <c r="O96">
-        <v>-54.49448072000003</v>
+        <v>-55.21569860000002</v>
       </c>
       <c r="P96">
-        <v>-217.9779228800001</v>
+        <v>-220.8627944000001</v>
       </c>
       <c r="Q96">
-        <v>-173.1779228800001</v>
+        <v>-176.0627944000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5349341599541731</v>
+        <v>0.632760991945008</v>
       </c>
       <c r="T96">
-        <v>9.278694268076331</v>
+        <v>11.1344331216916</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03923623238573276</v>
+        <v>0.03882321941325137</v>
       </c>
       <c r="W96">
-        <v>0.2265480964034442</v>
+        <v>0.2266454848623553</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1961811619286637</v>
+        <v>0.1941160970662568</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2469512602164879</v>
+        <v>0.2488512602164879</v>
       </c>
       <c r="C97">
-        <v>-1209.768289748571</v>
+        <v>-1227.008220533715</v>
       </c>
       <c r="D97">
-        <v>208.0667102514292</v>
+        <v>206.1197794662858</v>
       </c>
       <c r="E97">
-        <v>678.7350000000001</v>
+        <v>694.0280000000002</v>
       </c>
       <c r="F97">
-        <v>1452.835</v>
+        <v>1468.128</v>
       </c>
       <c r="G97">
         <v>35</v>
@@ -9235,37 +9235,37 @@
         <v>66.5</v>
       </c>
       <c r="M97">
-        <v>342.5784930000001</v>
+        <v>346.1845824000001</v>
       </c>
       <c r="N97">
-        <v>-276.0784930000001</v>
+        <v>-279.6845824000001</v>
       </c>
       <c r="O97">
-        <v>-55.21569860000002</v>
+        <v>-55.93691648000003</v>
       </c>
       <c r="P97">
-        <v>-220.8627944000001</v>
+        <v>-223.7476659200001</v>
       </c>
       <c r="Q97">
-        <v>-176.0627944000001</v>
+        <v>-178.9476659200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.632760991945008</v>
+        <v>0.7795012399312603</v>
       </c>
       <c r="T97">
-        <v>11.1344331216916</v>
+        <v>13.91804140211451</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03882321941325137</v>
+        <v>0.03841881087769666</v>
       </c>
       <c r="W97">
-        <v>0.2266454848623553</v>
+        <v>0.2267408443950391</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1941160970662568</v>
+        <v>0.1920940543884833</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2488512602164879</v>
+        <v>0.250751260216488</v>
       </c>
       <c r="C98">
-        <v>-1227.008220533715</v>
+        <v>-1244.212053287669</v>
       </c>
       <c r="D98">
-        <v>206.1197794662856</v>
+        <v>204.2089467123308</v>
       </c>
       <c r="E98">
-        <v>694.028</v>
+        <v>709.3209999999999</v>
       </c>
       <c r="F98">
-        <v>1468.128</v>
+        <v>1483.421</v>
       </c>
       <c r="G98">
         <v>35</v>
@@ -9317,37 +9317,37 @@
         <v>66.5</v>
       </c>
       <c r="M98">
-        <v>346.1845824000001</v>
+        <v>349.7906718</v>
       </c>
       <c r="N98">
-        <v>-279.6845824000001</v>
+        <v>-283.2906718</v>
       </c>
       <c r="O98">
-        <v>-55.93691648000001</v>
+        <v>-56.65813436000001</v>
       </c>
       <c r="P98">
-        <v>-223.7476659200001</v>
+        <v>-226.63253744</v>
       </c>
       <c r="Q98">
-        <v>-178.9476659200001</v>
+        <v>-181.83253744</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7795012399312583</v>
+        <v>1.024068319908345</v>
       </c>
       <c r="T98">
-        <v>13.91804140211447</v>
+        <v>18.55738853615263</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03841881087769666</v>
+        <v>0.03802274066246269</v>
       </c>
       <c r="W98">
-        <v>0.2267408443950391</v>
+        <v>0.2268342377517913</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1920940543884834</v>
+        <v>0.1901137033123134</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.250751260216488</v>
+        <v>0.2526512602164879</v>
       </c>
       <c r="C99">
-        <v>-1244.212053287669</v>
+        <v>-1261.380782728947</v>
       </c>
       <c r="D99">
-        <v>204.2089467123308</v>
+        <v>202.3332172710533</v>
       </c>
       <c r="E99">
-        <v>709.3209999999999</v>
+        <v>724.614</v>
       </c>
       <c r="F99">
-        <v>1483.421</v>
+        <v>1498.714</v>
       </c>
       <c r="G99">
         <v>35</v>
@@ -9399,37 +9399,37 @@
         <v>66.5</v>
       </c>
       <c r="M99">
-        <v>349.7906718</v>
+        <v>353.3967612000001</v>
       </c>
       <c r="N99">
-        <v>-283.2906718</v>
+        <v>-286.8967612000001</v>
       </c>
       <c r="O99">
-        <v>-56.65813436000001</v>
+        <v>-57.37935224000002</v>
       </c>
       <c r="P99">
-        <v>-226.63253744</v>
+        <v>-229.5174089600001</v>
       </c>
       <c r="Q99">
-        <v>-181.83253744</v>
+        <v>-184.7174089600001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.024068319908345</v>
+        <v>1.513202479862517</v>
       </c>
       <c r="T99">
-        <v>18.55738853615263</v>
+        <v>27.83608280422894</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03802274066246269</v>
+        <v>0.03763475351284572</v>
       </c>
       <c r="W99">
-        <v>0.2268342377517913</v>
+        <v>0.226925725121671</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1901137033123134</v>
+        <v>0.1881737675642285</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2526512602164879</v>
+        <v>0.2545512602164879</v>
       </c>
       <c r="C100">
-        <v>-1261.380782728947</v>
+        <v>-1278.515367361376</v>
       </c>
       <c r="D100">
-        <v>202.3332172710533</v>
+        <v>200.4916326386238</v>
       </c>
       <c r="E100">
-        <v>724.614</v>
+        <v>739.9069999999999</v>
       </c>
       <c r="F100">
-        <v>1498.714</v>
+        <v>1514.007</v>
       </c>
       <c r="G100">
         <v>35</v>
@@ -9481,37 +9481,37 @@
         <v>66.5</v>
       </c>
       <c r="M100">
-        <v>353.3967612000001</v>
+        <v>357.0028506</v>
       </c>
       <c r="N100">
-        <v>-286.8967612000001</v>
+        <v>-290.5028506</v>
       </c>
       <c r="O100">
-        <v>-57.37935224000002</v>
+        <v>-58.10057012000001</v>
       </c>
       <c r="P100">
-        <v>-229.5174089600001</v>
+        <v>-232.40228048</v>
       </c>
       <c r="Q100">
-        <v>-184.7174089600001</v>
+        <v>-187.60228048</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.513202479862517</v>
+        <v>2.980604959725033</v>
       </c>
       <c r="T100">
-        <v>27.83608280422894</v>
+        <v>55.67216560845788</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03763475351284572</v>
+        <v>0.03725460448746343</v>
       </c>
       <c r="W100">
-        <v>0.226925725121671</v>
+        <v>0.2270153642618561</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1881737675642285</v>
+        <v>0.1862730224373171</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2545512602164879</v>
-      </c>
-      <c r="C101">
-        <v>-1278.515367361376</v>
-      </c>
-      <c r="D101">
-        <v>200.4916326386238</v>
-      </c>
-      <c r="E101">
-        <v>739.9069999999999</v>
-      </c>
-      <c r="F101">
-        <v>1514.007</v>
-      </c>
-      <c r="G101">
-        <v>35</v>
-      </c>
-      <c r="H101">
-        <v>755.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>111.3</v>
-      </c>
-      <c r="K101">
-        <v>44.8</v>
-      </c>
-      <c r="L101">
-        <v>66.5</v>
-      </c>
-      <c r="M101">
-        <v>357.0028506</v>
-      </c>
-      <c r="N101">
-        <v>-290.5028506</v>
-      </c>
-      <c r="O101">
-        <v>-58.10057012000001</v>
-      </c>
-      <c r="P101">
-        <v>-232.40228048</v>
-      </c>
-      <c r="Q101">
-        <v>-187.60228048</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.980604959725033</v>
-      </c>
-      <c r="T101">
-        <v>55.67216560845788</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03725460448746343</v>
-      </c>
-      <c r="W101">
-        <v>0.2270153642618561</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1862730224373171</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
